--- a/Informe tecnico/costos finales.xlsx
+++ b/Informe tecnico/costos finales.xlsx
@@ -1,596 +1,124 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sena\Monitor-de-consumo\Documentacion-proyecto-Monitor-de-consumo-electrico\Informe tecnico\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" firstSheet="1" activeTab="2"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" tabRatio="600" firstSheet="1" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1.Resumen" sheetId="1" r:id="rId1"/>
-    <sheet name="5.Diagrama de gantt" sheetId="2" r:id="rId2"/>
-    <sheet name="costos del equipo de trabajo" sheetId="3" r:id="rId3"/>
-    <sheet name="costos estimados para usuarios" sheetId="4" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.Diagrama de gantt" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="costos del equipo de trabajo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="costos estimados para usuarios" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="Pz3iwk33jnOiIPCKBtoSzWvzhcyR2oF1QmG3ZwfGeKY="/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="136">
-  <si>
-    <t>Resumen Ejecutivo Ppto</t>
-  </si>
-  <si>
-    <t>ITEM</t>
-  </si>
-  <si>
-    <t>COSTOS</t>
-  </si>
-  <si>
-    <t>Hardware</t>
-  </si>
-  <si>
-    <t>Software</t>
-  </si>
-  <si>
-    <t>Rec. Humano</t>
-  </si>
-  <si>
-    <t>Otros</t>
-  </si>
-  <si>
-    <t>ENERO</t>
-  </si>
-  <si>
-    <t>FEBRERO</t>
-  </si>
-  <si>
-    <t>MARZO</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>MAYO</t>
-  </si>
-  <si>
-    <t>JUNIO</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
-    <t>Analsis</t>
-  </si>
-  <si>
-    <t>Elicitación</t>
-  </si>
-  <si>
-    <t>Análisis</t>
-  </si>
-  <si>
-    <t>Informe de analisis (SRS)</t>
-  </si>
-  <si>
-    <t>Validación de requerimientos</t>
-  </si>
-  <si>
-    <t>Planeación</t>
-  </si>
-  <si>
-    <t>Crear arquitectura</t>
-  </si>
-  <si>
-    <t>Seleccionar tecnologias</t>
-  </si>
-  <si>
-    <t>Disgramas UML</t>
-  </si>
-  <si>
-    <t>Diseñar la UI de la app y Informe de diseño</t>
-  </si>
-  <si>
-    <t>Desarrollo</t>
-  </si>
-  <si>
-    <t>Configuración de entorno</t>
-  </si>
-  <si>
-    <t>Desarrollo de prototipo físico (HW)</t>
-  </si>
-  <si>
-    <t>Desarrollo de backend (API / lógica de negocio)</t>
-  </si>
-  <si>
-    <t>Desarrollo de frontend / app móvil</t>
-  </si>
-  <si>
-    <t>Integración HW–SW</t>
-  </si>
-  <si>
-    <t>Documentación técnica</t>
-  </si>
-  <si>
-    <t>IMPLEMENTACION</t>
-  </si>
-  <si>
-    <t>Pruebas unitarias</t>
-  </si>
-  <si>
-    <t>Pruebas de integración</t>
-  </si>
-  <si>
-    <t>Pruebas con usuarios finales</t>
-  </si>
-  <si>
-    <t>Corrección de errores</t>
-  </si>
-  <si>
-    <t>EVALUACION</t>
-  </si>
-  <si>
-    <t>Evaluación de desempeño del prototipo</t>
-  </si>
-  <si>
-    <t>Informe final de evaluación</t>
-  </si>
-  <si>
-    <t>Presentación y cierre del proyecto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Costos de Hardware </t>
-  </si>
-  <si>
-    <t>Costos de Software</t>
-  </si>
-  <si>
-    <t>Costos de Recurso Humano (estimado por 4 meses de desarrollo)</t>
-  </si>
-  <si>
-    <t>opciones de los pc para el equipo de desarrollo</t>
-  </si>
-  <si>
-    <t>Cantidad</t>
-  </si>
-  <si>
-    <t>Precio unitario (COP)</t>
-  </si>
-  <si>
-    <t>Subtotal (COP)</t>
-  </si>
-  <si>
-    <t>Herramienta</t>
-  </si>
-  <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>Costo estimado</t>
-  </si>
-  <si>
-    <t>Rol</t>
-  </si>
-  <si>
-    <t>Tiempo (meses)</t>
-  </si>
-  <si>
-    <t>Costo mensual aprox. (COP)</t>
-  </si>
-  <si>
-    <t>Característica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opción 1: Gama de entrada </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opción 2: Gama media </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opción 3: Gama alta </t>
-  </si>
-  <si>
-    <t>ESP32 (WiFi + Bluetooth)</t>
-  </si>
-  <si>
-    <t>Arduino IDE</t>
-  </si>
-  <si>
-    <t>Libre</t>
-  </si>
-  <si>
-    <t>lider</t>
-  </si>
-  <si>
-    <t>Rango de precios (COP)</t>
-  </si>
-  <si>
-    <t>$2.000.000 – $3.500.000</t>
-  </si>
-  <si>
-    <t>$3.500.000 – $6.000.000</t>
-  </si>
-  <si>
-    <t>$8.000.000 – $15.000.000+</t>
-  </si>
-  <si>
-    <t>Visual Studio Code</t>
-  </si>
-  <si>
-    <t>Desarrollador de software</t>
-  </si>
-  <si>
-    <t>Procesador (CPU)</t>
-  </si>
-  <si>
-    <t>Intel Core i5 / AMD Ryzen 5</t>
-  </si>
-  <si>
-    <t>Intel Core i7 / AMD Ryzen 7</t>
-  </si>
-  <si>
-    <t>Intel Core i9 / AMD Ryzen 9</t>
-  </si>
-  <si>
-    <t>Firebase</t>
-  </si>
-  <si>
-    <t>gestor de bases de datos</t>
-  </si>
-  <si>
-    <t>Memoria RAM</t>
-  </si>
-  <si>
-    <t>16 GB DDR4</t>
-  </si>
-  <si>
-    <t>32 GB DDR4</t>
-  </si>
-  <si>
-    <t>64 GB DDR4/DDR5</t>
-  </si>
-  <si>
-    <t>analista</t>
-  </si>
-  <si>
-    <t>Almacenamiento</t>
-  </si>
-  <si>
-    <t>512 GB SSD (SATA/NVMe)</t>
-  </si>
-  <si>
-    <t>1 TB SSD</t>
-  </si>
-  <si>
-    <t>2 TB SSD NVMe</t>
-  </si>
-  <si>
-    <t>Total recurso humano</t>
-  </si>
-  <si>
-    <t>–</t>
-  </si>
-  <si>
-    <t>Tarjeta gráfica (GPU)</t>
-  </si>
-  <si>
-    <t>Integrada</t>
-  </si>
-  <si>
-    <t>Integrada o dedicada de gama baja (RTX 3050 / RX 6600)</t>
-  </si>
-  <si>
-    <t>Dedicada de gama alta (RTX 4080 o superior)</t>
-  </si>
-  <si>
-    <t>Caja o carcasa plástica (prototipo)</t>
-  </si>
-  <si>
-    <t>Justificación de costos</t>
-  </si>
-  <si>
-    <t>Componentes accesibles y estándar. No requiere GPU dedicada.</t>
-  </si>
-  <si>
-    <t>Mayor RAM, CPU más potente, almacenamiento ampliado. Posible inclusión de GPU de gama baja.</t>
-  </si>
-  <si>
-    <t>Componentes premium: CPU extremo, RAM de gran capacidad, SSD NVMe grande y GPU de última generación.</t>
-  </si>
-  <si>
-    <t>costos pc del equipo de desarrollo</t>
-  </si>
-  <si>
-    <t>Ejemplos de referencia</t>
-  </si>
-  <si>
-    <t>Clones y Periféricos, Mercado Libre, Todo Tintas y Suministros</t>
-  </si>
-  <si>
-    <t>Falabella, Mercado Libre, PC Ware Colombia</t>
-  </si>
-  <si>
-    <t>costos cel del equipo de desarrollo</t>
-  </si>
-  <si>
-    <t>opcion elegida</t>
-  </si>
-  <si>
-    <t>la opción de gama media es la más adecuada porque ofrece un equilibrio entre rendimiento, capacidad de expansión y costo, garantizando que el proyecto de monitoreo eléctrico pueda desarrollarse de manera eficiente y con proyección a futuro.</t>
-  </si>
-  <si>
-    <t>Total aproximado hardware</t>
-  </si>
-  <si>
-    <t>total</t>
-  </si>
-  <si>
-    <t>opcion de celular para desarrolladores</t>
-  </si>
-  <si>
-    <t>Modelo</t>
-  </si>
-  <si>
-    <t>Rango de precio (COP)</t>
-  </si>
-  <si>
-    <t>Fuente/Referencia</t>
-  </si>
-  <si>
-    <t>Xiaomi Redmi 13</t>
-  </si>
-  <si>
-    <t>$450.000 – $700.000</t>
-  </si>
-  <si>
-    <t>Mercado Libre y otras tiendas en línea</t>
-  </si>
-  <si>
-    <t>Samsung Galaxy A55</t>
-  </si>
-  <si>
-    <t>$1.600.000 – $2.200.000</t>
-  </si>
-  <si>
-    <t>Tiendas oficiales de operadores y minoristas (Mercado Libre, Movistar)</t>
-  </si>
-  <si>
-    <t>Apple iPhone 15 Pro (128 GB)</t>
-  </si>
-  <si>
-    <t>$4.500.000 – $5.000.000</t>
-  </si>
-  <si>
-    <t>Principales distribuidores oficiales (Mercado Libre, Movistar)</t>
-  </si>
-  <si>
-    <t>el Xiaomi Redmi 13 es la mejor elección porque combina bajo costo, compatibilidad tecnológica y accesibilidad en el mercado, cumpliendo con los requerimientos del proyecto sin generar gastos excesivos.</t>
-  </si>
-  <si>
-    <t>Celulares para Usuarios</t>
-  </si>
-  <si>
-    <t>Laptops para Usuarios</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>HP 240 G9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> (Core i5, 8 GB RAM, 512 GB SSD)</t>
-    </r>
-  </si>
-  <si>
-    <t>$2.500.000 – $2.900.000</t>
-  </si>
-  <si>
-    <t>HP Store Colombia, Mercado Libre</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Dell Inspiron 15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> (Core i5, 8 GB RAM)</t>
-    </r>
-  </si>
-  <si>
-    <t>$1.800.000 – $2.500.000</t>
-  </si>
-  <si>
-    <t>Dell.es (referencia), Mercado Libre</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Apple MacBook Air M2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> (8 GB RAM, 256 GB SSD)</t>
-    </r>
-  </si>
-  <si>
-    <t>$4.000.000 – $4.500.000</t>
-  </si>
-  <si>
-    <t>Éxito, Mercado Libre</t>
-  </si>
-  <si>
-    <t>Fuente de alimentación Ac-dc 3.3v Hlk-pm03</t>
-  </si>
-  <si>
-    <t>Cables Jumpers Macho Macho 20 cm</t>
-  </si>
-  <si>
-    <t>Cables Jumpers Macho Hembra 20 cm</t>
-  </si>
-  <si>
-    <t>Medidor de electricidad digital Peacefair PZEM-004T-100A (Sensor)</t>
-  </si>
-  <si>
-    <t>Cable eléctrico encauchetado de 2x14 AWG</t>
-  </si>
-  <si>
-    <t>Cables Jumpers Hembra Hembra 20 cm</t>
-  </si>
-  <si>
-    <t>Cable calibre 14 rojo y negro</t>
-  </si>
-  <si>
-    <t>Conector Jst Macho-Hembra Xh2.54 Xh2.54mm 4</t>
-  </si>
-  <si>
-    <t>Gratis</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="6">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="_-[$$-240A]\ * #,##0.00_-;\-[$$-240A]\ * #,##0.00_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@"/>
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@"/>
-    <numFmt numFmtId="166" formatCode="_-[$$-240A]\ * #,##0.00_-;\-[$$-240A]\ * #,##0.00_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="167" formatCode="_-[$$-240A]\ * #,##0.00_-;\-[$$-240A]\ * #,##0.00_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="15">
     <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="18"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="14"/>
-      <color theme="1"/>
-      <name val="Aptos"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="10">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -644,7 +172,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="44">
+  <borders count="51">
     <border>
       <left/>
       <right/>
@@ -1159,313 +687,544 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="8"/>
   </cellStyleXfs>
-  <cellXfs count="118">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="161">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="6" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="4" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1666,79 +1425,97 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:C1000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:C8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="10.7109375" customWidth="1"/>
-    <col min="3" max="3" width="28.140625" customWidth="1"/>
-    <col min="4" max="26" width="10.7109375" customWidth="1"/>
+    <col width="10.7109375" customWidth="1" min="1" max="2"/>
+    <col width="28.140625" customWidth="1" min="3" max="3"/>
+    <col width="10.7109375" customWidth="1" min="4" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" ht="14.25" customHeight="1"/>
-    <row r="2" spans="2:3" ht="14.25" customHeight="1">
-      <c r="B2" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="44"/>
+    <row r="1" ht="14.25" customHeight="1"/>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="B2" s="118" t="inlineStr">
+        <is>
+          <t>Resumen Ejecutivo Ppto</t>
+        </is>
+      </c>
+      <c r="C2" s="119" t="n"/>
     </row>
-    <row r="3" spans="2:3" ht="14.25" customHeight="1">
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>2</v>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>ITEM</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>COSTOS</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="14.25" customHeight="1">
-      <c r="B4" s="2" t="s">
-        <v>3</v>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
       </c>
       <c r="C4" s="3">
         <f>'costos del equipo de trabajo'!E16</f>
-        <v>8073997</v>
+        <v/>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="14.25" customHeight="1">
-      <c r="B5" s="2" t="s">
-        <v>4</v>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
       </c>
       <c r="C5" s="4">
         <f>'costos del equipo de trabajo'!I7</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="14.25" customHeight="1">
-      <c r="B6" s="2" t="s">
-        <v>5</v>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Rec. Humano</t>
+        </is>
       </c>
       <c r="C6" s="4">
         <f>'costos del equipo de trabajo'!O8</f>
-        <v>48900000</v>
+        <v/>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="14.25" customHeight="1">
-      <c r="B7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="4">
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="14.25" customHeight="1">
+    <row r="8" ht="14.25" customHeight="1">
       <c r="C8" s="5">
         <f>SUM(C4:C6)</f>
-        <v>56973997</v>
+        <v/>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="14.25" customHeight="1"/>
-    <row r="10" spans="2:3" ht="14.25" customHeight="1"/>
-    <row r="11" spans="2:3" ht="14.25" customHeight="1"/>
-    <row r="12" spans="2:3" ht="14.25" customHeight="1"/>
-    <row r="13" spans="2:3" ht="14.25" customHeight="1"/>
-    <row r="14" spans="2:3" ht="14.25" customHeight="1"/>
-    <row r="15" spans="2:3" ht="14.25" customHeight="1"/>
-    <row r="16" spans="2:3" ht="14.25" customHeight="1"/>
+    <row r="9" ht="14.25" customHeight="1"/>
+    <row r="10" ht="14.25" customHeight="1"/>
+    <row r="11" ht="14.25" customHeight="1"/>
+    <row r="12" ht="14.25" customHeight="1"/>
+    <row r="13" ht="14.25" customHeight="1"/>
+    <row r="14" ht="14.25" customHeight="1"/>
+    <row r="15" ht="14.25" customHeight="1"/>
+    <row r="16" ht="14.25" customHeight="1"/>
     <row r="17" ht="14.25" customHeight="1"/>
     <row r="18" ht="14.25" customHeight="1"/>
     <row r="19" ht="14.25" customHeight="1"/>
@@ -2733,924 +2510,996 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:AE1000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:AE25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="10.7109375" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" customWidth="1"/>
-    <col min="4" max="4" width="5.28515625" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" customWidth="1"/>
-    <col min="6" max="6" width="5" customWidth="1"/>
-    <col min="7" max="7" width="5.42578125" customWidth="1"/>
-    <col min="8" max="9" width="5.28515625" customWidth="1"/>
-    <col min="10" max="10" width="5.140625" customWidth="1"/>
-    <col min="11" max="13" width="5.28515625" customWidth="1"/>
-    <col min="14" max="15" width="5" customWidth="1"/>
-    <col min="16" max="17" width="5.28515625" customWidth="1"/>
-    <col min="18" max="18" width="5" customWidth="1"/>
-    <col min="19" max="19" width="5.28515625" customWidth="1"/>
-    <col min="20" max="20" width="5.140625" customWidth="1"/>
-    <col min="21" max="26" width="5.28515625" customWidth="1"/>
-    <col min="27" max="31" width="5.42578125" customWidth="1"/>
+    <col width="10.7109375" customWidth="1" min="1" max="2"/>
+    <col width="24.7109375" customWidth="1" min="3" max="3"/>
+    <col width="5.28515625" customWidth="1" min="4" max="4"/>
+    <col width="5.140625" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5.42578125" customWidth="1" min="7" max="7"/>
+    <col width="5.28515625" customWidth="1" min="8" max="9"/>
+    <col width="5.140625" customWidth="1" min="10" max="10"/>
+    <col width="5.28515625" customWidth="1" min="11" max="13"/>
+    <col width="5" customWidth="1" min="14" max="15"/>
+    <col width="5.28515625" customWidth="1" min="16" max="17"/>
+    <col width="5" customWidth="1" min="18" max="18"/>
+    <col width="5.28515625" customWidth="1" min="19" max="19"/>
+    <col width="5.140625" customWidth="1" min="20" max="20"/>
+    <col width="5.28515625" customWidth="1" min="21" max="26"/>
+    <col width="5.42578125" customWidth="1" min="27" max="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:31" ht="14.25" customHeight="1"/>
-    <row r="2" spans="2:31" ht="14.25" customHeight="1">
-      <c r="D2" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="44"/>
-      <c r="T2" s="45" t="s">
-        <v>11</v>
-      </c>
-      <c r="U2" s="46"/>
-      <c r="V2" s="46"/>
-      <c r="W2" s="44"/>
-      <c r="X2" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y2" s="46"/>
-      <c r="Z2" s="46"/>
-      <c r="AA2" s="44"/>
-      <c r="AB2" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC2" s="46"/>
-      <c r="AD2" s="46"/>
-      <c r="AE2" s="44"/>
+    <row r="1" ht="14.25" customHeight="1"/>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="D2" s="120" t="inlineStr">
+        <is>
+          <t>ENERO</t>
+        </is>
+      </c>
+      <c r="E2" s="121" t="n"/>
+      <c r="F2" s="121" t="n"/>
+      <c r="G2" s="119" t="n"/>
+      <c r="H2" s="120" t="inlineStr">
+        <is>
+          <t>FEBRERO</t>
+        </is>
+      </c>
+      <c r="I2" s="121" t="n"/>
+      <c r="J2" s="121" t="n"/>
+      <c r="K2" s="119" t="n"/>
+      <c r="L2" s="120" t="inlineStr">
+        <is>
+          <t>MARZO</t>
+        </is>
+      </c>
+      <c r="M2" s="121" t="n"/>
+      <c r="N2" s="121" t="n"/>
+      <c r="O2" s="119" t="n"/>
+      <c r="P2" s="120" t="inlineStr">
+        <is>
+          <t>ABRIL</t>
+        </is>
+      </c>
+      <c r="Q2" s="121" t="n"/>
+      <c r="R2" s="121" t="n"/>
+      <c r="S2" s="119" t="n"/>
+      <c r="T2" s="120" t="inlineStr">
+        <is>
+          <t>MAYO</t>
+        </is>
+      </c>
+      <c r="U2" s="121" t="n"/>
+      <c r="V2" s="121" t="n"/>
+      <c r="W2" s="119" t="n"/>
+      <c r="X2" s="120" t="inlineStr">
+        <is>
+          <t>JUNIO</t>
+        </is>
+      </c>
+      <c r="Y2" s="121" t="n"/>
+      <c r="Z2" s="121" t="n"/>
+      <c r="AA2" s="119" t="n"/>
+      <c r="AB2" s="120" t="inlineStr">
+        <is>
+          <t>JULIO</t>
+        </is>
+      </c>
+      <c r="AC2" s="121" t="n"/>
+      <c r="AD2" s="121" t="n"/>
+      <c r="AE2" s="119" t="n"/>
     </row>
-    <row r="3" spans="2:31" ht="14.25" customHeight="1">
-      <c r="D3" s="6">
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="D3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="N3" s="6">
+      <c r="N3" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="O3" s="6">
+      <c r="O3" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" s="6">
+      <c r="Q3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="R3" s="6">
+      <c r="R3" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="S3" s="6">
+      <c r="S3" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="T3" s="6">
+      <c r="T3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="U3" s="6">
+      <c r="U3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="V3" s="6">
+      <c r="V3" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="W3" s="6">
+      <c r="W3" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="X3" s="6">
+      <c r="X3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="Y3" s="6">
+      <c r="Y3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="Z3" s="6">
+      <c r="Z3" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="AA3" s="6">
+      <c r="AA3" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="AB3" s="6">
+      <c r="AB3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="AC3" s="6">
+      <c r="AC3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="AD3" s="6">
+      <c r="AD3" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="AE3" s="6">
+      <c r="AE3" s="6" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:31" ht="14.25" customHeight="1">
-      <c r="B4" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="9"/>
-      <c r="X4" s="9"/>
-      <c r="Y4" s="9"/>
-      <c r="Z4" s="9"/>
-      <c r="AA4" s="9"/>
-      <c r="AB4" s="9"/>
-      <c r="AC4" s="9"/>
-      <c r="AD4" s="9"/>
-      <c r="AE4" s="9"/>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="B4" s="122" t="inlineStr">
+        <is>
+          <t>Analsis</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Elicitación</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="9" t="n"/>
+      <c r="H4" s="9" t="n"/>
+      <c r="I4" s="9" t="n"/>
+      <c r="J4" s="9" t="n"/>
+      <c r="K4" s="9" t="n"/>
+      <c r="L4" s="9" t="n"/>
+      <c r="M4" s="9" t="n"/>
+      <c r="N4" s="9" t="n"/>
+      <c r="O4" s="9" t="n"/>
+      <c r="P4" s="9" t="n"/>
+      <c r="Q4" s="9" t="n"/>
+      <c r="R4" s="9" t="n"/>
+      <c r="S4" s="9" t="n"/>
+      <c r="T4" s="9" t="n"/>
+      <c r="U4" s="9" t="n"/>
+      <c r="V4" s="9" t="n"/>
+      <c r="W4" s="9" t="n"/>
+      <c r="X4" s="9" t="n"/>
+      <c r="Y4" s="9" t="n"/>
+      <c r="Z4" s="9" t="n"/>
+      <c r="AA4" s="9" t="n"/>
+      <c r="AB4" s="9" t="n"/>
+      <c r="AC4" s="9" t="n"/>
+      <c r="AD4" s="9" t="n"/>
+      <c r="AE4" s="9" t="n"/>
     </row>
-    <row r="5" spans="2:31" ht="14.25" customHeight="1">
-      <c r="B5" s="48"/>
-      <c r="C5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="9"/>
-      <c r="Z5" s="9"/>
-      <c r="AA5" s="9"/>
-      <c r="AB5" s="9"/>
-      <c r="AC5" s="9"/>
-      <c r="AD5" s="9"/>
-      <c r="AE5" s="9"/>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="B5" s="123" t="n"/>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="9" t="n"/>
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" s="9" t="n"/>
+      <c r="M5" s="9" t="n"/>
+      <c r="N5" s="9" t="n"/>
+      <c r="O5" s="9" t="n"/>
+      <c r="P5" s="9" t="n"/>
+      <c r="Q5" s="9" t="n"/>
+      <c r="R5" s="9" t="n"/>
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="9" t="n"/>
+      <c r="U5" s="9" t="n"/>
+      <c r="V5" s="9" t="n"/>
+      <c r="W5" s="9" t="n"/>
+      <c r="X5" s="9" t="n"/>
+      <c r="Y5" s="9" t="n"/>
+      <c r="Z5" s="9" t="n"/>
+      <c r="AA5" s="9" t="n"/>
+      <c r="AB5" s="9" t="n"/>
+      <c r="AC5" s="9" t="n"/>
+      <c r="AD5" s="9" t="n"/>
+      <c r="AE5" s="9" t="n"/>
     </row>
-    <row r="6" spans="2:31" ht="14.25" customHeight="1">
-      <c r="B6" s="48"/>
-      <c r="C6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="9"/>
-      <c r="AE6" s="9"/>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="B6" s="123" t="n"/>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Informe de analisis (SRS)</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="9" t="n"/>
+      <c r="J6" s="9" t="n"/>
+      <c r="K6" s="9" t="n"/>
+      <c r="L6" s="9" t="n"/>
+      <c r="M6" s="9" t="n"/>
+      <c r="N6" s="9" t="n"/>
+      <c r="O6" s="9" t="n"/>
+      <c r="P6" s="9" t="n"/>
+      <c r="Q6" s="9" t="n"/>
+      <c r="R6" s="9" t="n"/>
+      <c r="S6" s="9" t="n"/>
+      <c r="T6" s="9" t="n"/>
+      <c r="U6" s="9" t="n"/>
+      <c r="V6" s="9" t="n"/>
+      <c r="W6" s="9" t="n"/>
+      <c r="X6" s="9" t="n"/>
+      <c r="Y6" s="9" t="n"/>
+      <c r="Z6" s="9" t="n"/>
+      <c r="AA6" s="9" t="n"/>
+      <c r="AB6" s="9" t="n"/>
+      <c r="AC6" s="9" t="n"/>
+      <c r="AD6" s="9" t="n"/>
+      <c r="AE6" s="9" t="n"/>
     </row>
-    <row r="7" spans="2:31" ht="14.25" customHeight="1">
-      <c r="B7" s="49"/>
-      <c r="C7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
-      <c r="T7" s="9"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="9"/>
-      <c r="Z7" s="9"/>
-      <c r="AA7" s="9"/>
-      <c r="AB7" s="9"/>
-      <c r="AC7" s="9"/>
-      <c r="AD7" s="9"/>
-      <c r="AE7" s="9"/>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="B7" s="124" t="n"/>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Validación de requerimientos</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="9" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="9" t="n"/>
+      <c r="K7" s="9" t="n"/>
+      <c r="L7" s="9" t="n"/>
+      <c r="M7" s="9" t="n"/>
+      <c r="N7" s="9" t="n"/>
+      <c r="O7" s="9" t="n"/>
+      <c r="P7" s="9" t="n"/>
+      <c r="Q7" s="9" t="n"/>
+      <c r="R7" s="9" t="n"/>
+      <c r="S7" s="9" t="n"/>
+      <c r="T7" s="9" t="n"/>
+      <c r="U7" s="9" t="n"/>
+      <c r="V7" s="9" t="n"/>
+      <c r="W7" s="9" t="n"/>
+      <c r="X7" s="9" t="n"/>
+      <c r="Y7" s="9" t="n"/>
+      <c r="Z7" s="9" t="n"/>
+      <c r="AA7" s="9" t="n"/>
+      <c r="AB7" s="9" t="n"/>
+      <c r="AC7" s="9" t="n"/>
+      <c r="AD7" s="9" t="n"/>
+      <c r="AE7" s="9" t="n"/>
     </row>
-    <row r="8" spans="2:31" ht="14.25" customHeight="1">
-      <c r="B8" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="9"/>
-      <c r="U8" s="9"/>
-      <c r="V8" s="9"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="9"/>
-      <c r="Y8" s="9"/>
-      <c r="Z8" s="9"/>
-      <c r="AA8" s="9"/>
-      <c r="AB8" s="9"/>
-      <c r="AC8" s="9"/>
-      <c r="AD8" s="9"/>
-      <c r="AE8" s="9"/>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="B8" s="122" t="inlineStr">
+        <is>
+          <t>Planeación</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Crear arquitectura</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="9" t="n"/>
+      <c r="L8" s="9" t="n"/>
+      <c r="M8" s="9" t="n"/>
+      <c r="N8" s="9" t="n"/>
+      <c r="O8" s="9" t="n"/>
+      <c r="P8" s="9" t="n"/>
+      <c r="Q8" s="9" t="n"/>
+      <c r="R8" s="9" t="n"/>
+      <c r="S8" s="9" t="n"/>
+      <c r="T8" s="9" t="n"/>
+      <c r="U8" s="9" t="n"/>
+      <c r="V8" s="9" t="n"/>
+      <c r="W8" s="9" t="n"/>
+      <c r="X8" s="9" t="n"/>
+      <c r="Y8" s="9" t="n"/>
+      <c r="Z8" s="9" t="n"/>
+      <c r="AA8" s="9" t="n"/>
+      <c r="AB8" s="9" t="n"/>
+      <c r="AC8" s="9" t="n"/>
+      <c r="AD8" s="9" t="n"/>
+      <c r="AE8" s="9" t="n"/>
     </row>
-    <row r="9" spans="2:31" ht="14.25" customHeight="1">
-      <c r="B9" s="48"/>
-      <c r="C9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="9"/>
-      <c r="Y9" s="9"/>
-      <c r="Z9" s="9"/>
-      <c r="AA9" s="9"/>
-      <c r="AB9" s="9"/>
-      <c r="AC9" s="9"/>
-      <c r="AD9" s="9"/>
-      <c r="AE9" s="9"/>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="B9" s="123" t="n"/>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Seleccionar tecnologias</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="9" t="n"/>
+      <c r="I9" s="9" t="n"/>
+      <c r="J9" s="9" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="9" t="n"/>
+      <c r="M9" s="9" t="n"/>
+      <c r="N9" s="9" t="n"/>
+      <c r="O9" s="9" t="n"/>
+      <c r="P9" s="9" t="n"/>
+      <c r="Q9" s="9" t="n"/>
+      <c r="R9" s="9" t="n"/>
+      <c r="S9" s="9" t="n"/>
+      <c r="T9" s="9" t="n"/>
+      <c r="U9" s="9" t="n"/>
+      <c r="V9" s="9" t="n"/>
+      <c r="W9" s="9" t="n"/>
+      <c r="X9" s="9" t="n"/>
+      <c r="Y9" s="9" t="n"/>
+      <c r="Z9" s="9" t="n"/>
+      <c r="AA9" s="9" t="n"/>
+      <c r="AB9" s="9" t="n"/>
+      <c r="AC9" s="9" t="n"/>
+      <c r="AD9" s="9" t="n"/>
+      <c r="AE9" s="9" t="n"/>
     </row>
-    <row r="10" spans="2:31" ht="14.25" customHeight="1">
-      <c r="B10" s="48"/>
-      <c r="C10" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="9"/>
-      <c r="U10" s="9"/>
-      <c r="V10" s="9"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="9"/>
-      <c r="Y10" s="9"/>
-      <c r="Z10" s="9"/>
-      <c r="AA10" s="9"/>
-      <c r="AB10" s="9"/>
-      <c r="AC10" s="9"/>
-      <c r="AD10" s="9"/>
-      <c r="AE10" s="9"/>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="B10" s="123" t="n"/>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Disgramas UML</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="n"/>
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="9" t="n"/>
+      <c r="K10" s="9" t="n"/>
+      <c r="L10" s="12" t="n"/>
+      <c r="M10" s="9" t="n"/>
+      <c r="N10" s="9" t="n"/>
+      <c r="O10" s="9" t="n"/>
+      <c r="P10" s="9" t="n"/>
+      <c r="Q10" s="9" t="n"/>
+      <c r="R10" s="9" t="n"/>
+      <c r="S10" s="9" t="n"/>
+      <c r="T10" s="9" t="n"/>
+      <c r="U10" s="9" t="n"/>
+      <c r="V10" s="9" t="n"/>
+      <c r="W10" s="9" t="n"/>
+      <c r="X10" s="9" t="n"/>
+      <c r="Y10" s="9" t="n"/>
+      <c r="Z10" s="9" t="n"/>
+      <c r="AA10" s="9" t="n"/>
+      <c r="AB10" s="9" t="n"/>
+      <c r="AC10" s="9" t="n"/>
+      <c r="AD10" s="9" t="n"/>
+      <c r="AE10" s="9" t="n"/>
     </row>
-    <row r="11" spans="2:31" ht="29.25" customHeight="1">
-      <c r="B11" s="49"/>
-      <c r="C11" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="9"/>
-      <c r="Z11" s="9"/>
-      <c r="AA11" s="9"/>
-      <c r="AB11" s="9"/>
-      <c r="AC11" s="9"/>
-      <c r="AD11" s="9"/>
-      <c r="AE11" s="9"/>
+    <row r="11" ht="29.25" customHeight="1">
+      <c r="B11" s="124" t="n"/>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Diseñar la UI de la app y Informe de diseño</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="9" t="n"/>
+      <c r="L11" s="9" t="n"/>
+      <c r="M11" s="12" t="n"/>
+      <c r="N11" s="9" t="n"/>
+      <c r="O11" s="9" t="n"/>
+      <c r="P11" s="9" t="n"/>
+      <c r="Q11" s="9" t="n"/>
+      <c r="R11" s="9" t="n"/>
+      <c r="S11" s="9" t="n"/>
+      <c r="T11" s="9" t="n"/>
+      <c r="U11" s="9" t="n"/>
+      <c r="V11" s="9" t="n"/>
+      <c r="W11" s="9" t="n"/>
+      <c r="X11" s="9" t="n"/>
+      <c r="Y11" s="9" t="n"/>
+      <c r="Z11" s="9" t="n"/>
+      <c r="AA11" s="9" t="n"/>
+      <c r="AB11" s="9" t="n"/>
+      <c r="AC11" s="9" t="n"/>
+      <c r="AD11" s="9" t="n"/>
+      <c r="AE11" s="9" t="n"/>
     </row>
-    <row r="12" spans="2:31" ht="14.25" customHeight="1">
-      <c r="B12" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
-      <c r="T12" s="9"/>
-      <c r="U12" s="9"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9"/>
-      <c r="AA12" s="9"/>
-      <c r="AB12" s="9"/>
-      <c r="AC12" s="9"/>
-      <c r="AD12" s="9"/>
-      <c r="AE12" s="9"/>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="B12" s="122" t="inlineStr">
+        <is>
+          <t>Desarrollo</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Configuración de entorno</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="9" t="n"/>
+      <c r="I12" s="9" t="n"/>
+      <c r="J12" s="9" t="n"/>
+      <c r="K12" s="9" t="n"/>
+      <c r="L12" s="9" t="n"/>
+      <c r="M12" s="9" t="n"/>
+      <c r="N12" s="15" t="n"/>
+      <c r="O12" s="9" t="n"/>
+      <c r="P12" s="9" t="n"/>
+      <c r="Q12" s="9" t="n"/>
+      <c r="R12" s="9" t="n"/>
+      <c r="S12" s="9" t="n"/>
+      <c r="T12" s="9" t="n"/>
+      <c r="U12" s="9" t="n"/>
+      <c r="V12" s="9" t="n"/>
+      <c r="W12" s="9" t="n"/>
+      <c r="X12" s="9" t="n"/>
+      <c r="Y12" s="9" t="n"/>
+      <c r="Z12" s="9" t="n"/>
+      <c r="AA12" s="9" t="n"/>
+      <c r="AB12" s="9" t="n"/>
+      <c r="AC12" s="9" t="n"/>
+      <c r="AD12" s="9" t="n"/>
+      <c r="AE12" s="9" t="n"/>
     </row>
-    <row r="13" spans="2:31" ht="28.5" customHeight="1">
-      <c r="B13" s="48"/>
-      <c r="C13" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="9"/>
-      <c r="AE13" s="9"/>
+    <row r="13" ht="28.5" customHeight="1">
+      <c r="B13" s="123" t="n"/>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>Desarrollo de prototipo físico (HW)</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="9" t="n"/>
+      <c r="I13" s="9" t="n"/>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="9" t="n"/>
+      <c r="L13" s="9" t="n"/>
+      <c r="M13" s="9" t="n"/>
+      <c r="N13" s="15" t="n"/>
+      <c r="O13" s="15" t="n"/>
+      <c r="P13" s="15" t="n"/>
+      <c r="Q13" s="9" t="n"/>
+      <c r="R13" s="9" t="n"/>
+      <c r="S13" s="9" t="n"/>
+      <c r="T13" s="9" t="n"/>
+      <c r="U13" s="9" t="n"/>
+      <c r="V13" s="9" t="n"/>
+      <c r="W13" s="9" t="n"/>
+      <c r="X13" s="9" t="n"/>
+      <c r="Y13" s="9" t="n"/>
+      <c r="Z13" s="9" t="n"/>
+      <c r="AA13" s="9" t="n"/>
+      <c r="AB13" s="9" t="n"/>
+      <c r="AC13" s="9" t="n"/>
+      <c r="AD13" s="9" t="n"/>
+      <c r="AE13" s="9" t="n"/>
     </row>
-    <row r="14" spans="2:31" ht="31.5" customHeight="1">
-      <c r="B14" s="48"/>
-      <c r="C14" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="15"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="9"/>
-      <c r="U14" s="9"/>
-      <c r="V14" s="9"/>
-      <c r="W14" s="9"/>
-      <c r="X14" s="9"/>
-      <c r="Y14" s="9"/>
-      <c r="Z14" s="9"/>
-      <c r="AA14" s="9"/>
-      <c r="AB14" s="9"/>
-      <c r="AC14" s="9"/>
-      <c r="AD14" s="9"/>
-      <c r="AE14" s="9"/>
+    <row r="14" ht="31.5" customHeight="1">
+      <c r="B14" s="123" t="n"/>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>Desarrollo de backend (API / lógica de negocio)</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="9" t="n"/>
+      <c r="I14" s="9" t="n"/>
+      <c r="J14" s="9" t="n"/>
+      <c r="K14" s="9" t="n"/>
+      <c r="L14" s="9" t="n"/>
+      <c r="M14" s="9" t="n"/>
+      <c r="N14" s="9" t="n"/>
+      <c r="O14" s="9" t="n"/>
+      <c r="P14" s="15" t="n"/>
+      <c r="Q14" s="15" t="n"/>
+      <c r="R14" s="15" t="n"/>
+      <c r="S14" s="9" t="n"/>
+      <c r="T14" s="9" t="n"/>
+      <c r="U14" s="9" t="n"/>
+      <c r="V14" s="9" t="n"/>
+      <c r="W14" s="9" t="n"/>
+      <c r="X14" s="9" t="n"/>
+      <c r="Y14" s="9" t="n"/>
+      <c r="Z14" s="9" t="n"/>
+      <c r="AA14" s="9" t="n"/>
+      <c r="AB14" s="9" t="n"/>
+      <c r="AC14" s="9" t="n"/>
+      <c r="AD14" s="9" t="n"/>
+      <c r="AE14" s="9" t="n"/>
     </row>
-    <row r="15" spans="2:31" ht="28.5" customHeight="1">
-      <c r="B15" s="48"/>
-      <c r="C15" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="9"/>
-      <c r="R15" s="15"/>
-      <c r="S15" s="15"/>
-      <c r="T15" s="15"/>
-      <c r="U15" s="9"/>
-      <c r="V15" s="9"/>
-      <c r="W15" s="9"/>
-      <c r="X15" s="9"/>
-      <c r="Y15" s="9"/>
-      <c r="Z15" s="9"/>
-      <c r="AA15" s="9"/>
-      <c r="AB15" s="9"/>
-      <c r="AC15" s="9"/>
-      <c r="AD15" s="9"/>
-      <c r="AE15" s="9"/>
+    <row r="15" ht="28.5" customHeight="1">
+      <c r="B15" s="123" t="n"/>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Desarrollo de frontend / app móvil</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="n"/>
+      <c r="I15" s="9" t="n"/>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="9" t="n"/>
+      <c r="L15" s="9" t="n"/>
+      <c r="M15" s="9" t="n"/>
+      <c r="N15" s="9" t="n"/>
+      <c r="O15" s="9" t="n"/>
+      <c r="P15" s="9" t="n"/>
+      <c r="Q15" s="9" t="n"/>
+      <c r="R15" s="15" t="n"/>
+      <c r="S15" s="15" t="n"/>
+      <c r="T15" s="15" t="n"/>
+      <c r="U15" s="9" t="n"/>
+      <c r="V15" s="9" t="n"/>
+      <c r="W15" s="9" t="n"/>
+      <c r="X15" s="9" t="n"/>
+      <c r="Y15" s="9" t="n"/>
+      <c r="Z15" s="9" t="n"/>
+      <c r="AA15" s="9" t="n"/>
+      <c r="AB15" s="9" t="n"/>
+      <c r="AC15" s="9" t="n"/>
+      <c r="AD15" s="9" t="n"/>
+      <c r="AE15" s="9" t="n"/>
     </row>
-    <row r="16" spans="2:31" ht="14.25" customHeight="1">
-      <c r="B16" s="48"/>
-      <c r="C16" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="9"/>
-      <c r="S16" s="9"/>
-      <c r="T16" s="9"/>
-      <c r="U16" s="15"/>
-      <c r="V16" s="9"/>
-      <c r="W16" s="9"/>
-      <c r="X16" s="9"/>
-      <c r="Y16" s="9"/>
-      <c r="Z16" s="9"/>
-      <c r="AA16" s="9"/>
-      <c r="AB16" s="9"/>
-      <c r="AC16" s="9"/>
-      <c r="AD16" s="9"/>
-      <c r="AE16" s="9"/>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="B16" s="123" t="n"/>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Integración HW–SW</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="n"/>
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="n"/>
+      <c r="L16" s="9" t="n"/>
+      <c r="M16" s="9" t="n"/>
+      <c r="N16" s="9" t="n"/>
+      <c r="O16" s="9" t="n"/>
+      <c r="P16" s="9" t="n"/>
+      <c r="Q16" s="9" t="n"/>
+      <c r="R16" s="9" t="n"/>
+      <c r="S16" s="9" t="n"/>
+      <c r="T16" s="9" t="n"/>
+      <c r="U16" s="15" t="n"/>
+      <c r="V16" s="9" t="n"/>
+      <c r="W16" s="9" t="n"/>
+      <c r="X16" s="9" t="n"/>
+      <c r="Y16" s="9" t="n"/>
+      <c r="Z16" s="9" t="n"/>
+      <c r="AA16" s="9" t="n"/>
+      <c r="AB16" s="9" t="n"/>
+      <c r="AC16" s="9" t="n"/>
+      <c r="AD16" s="9" t="n"/>
+      <c r="AE16" s="9" t="n"/>
     </row>
-    <row r="17" spans="2:31" ht="14.25" customHeight="1">
-      <c r="B17" s="49"/>
-      <c r="C17" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="9"/>
-      <c r="U17" s="9"/>
-      <c r="V17" s="15"/>
-      <c r="W17" s="9"/>
-      <c r="X17" s="9"/>
-      <c r="Y17" s="9"/>
-      <c r="Z17" s="9"/>
-      <c r="AA17" s="9"/>
-      <c r="AB17" s="9"/>
-      <c r="AC17" s="9"/>
-      <c r="AD17" s="9"/>
-      <c r="AE17" s="9"/>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="B17" s="124" t="n"/>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Documentación técnica</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="9" t="n"/>
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="9" t="n"/>
+      <c r="L17" s="9" t="n"/>
+      <c r="M17" s="9" t="n"/>
+      <c r="N17" s="9" t="n"/>
+      <c r="O17" s="9" t="n"/>
+      <c r="P17" s="9" t="n"/>
+      <c r="Q17" s="9" t="n"/>
+      <c r="R17" s="9" t="n"/>
+      <c r="S17" s="9" t="n"/>
+      <c r="T17" s="9" t="n"/>
+      <c r="U17" s="9" t="n"/>
+      <c r="V17" s="15" t="n"/>
+      <c r="W17" s="9" t="n"/>
+      <c r="X17" s="9" t="n"/>
+      <c r="Y17" s="9" t="n"/>
+      <c r="Z17" s="9" t="n"/>
+      <c r="AA17" s="9" t="n"/>
+      <c r="AB17" s="9" t="n"/>
+      <c r="AC17" s="9" t="n"/>
+      <c r="AD17" s="9" t="n"/>
+      <c r="AE17" s="9" t="n"/>
     </row>
-    <row r="18" spans="2:31" ht="14.25" customHeight="1">
-      <c r="B18" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="9"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="9"/>
-      <c r="U18" s="9"/>
-      <c r="V18" s="9"/>
-      <c r="W18" s="18"/>
-      <c r="X18" s="9"/>
-      <c r="Y18" s="9"/>
-      <c r="Z18" s="9"/>
-      <c r="AA18" s="9"/>
-      <c r="AB18" s="9"/>
-      <c r="AC18" s="9"/>
-      <c r="AD18" s="9"/>
-      <c r="AE18" s="9"/>
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="B18" s="122" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACION</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>Pruebas unitarias</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="9" t="n"/>
+      <c r="I18" s="9" t="n"/>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="9" t="n"/>
+      <c r="L18" s="9" t="n"/>
+      <c r="M18" s="9" t="n"/>
+      <c r="N18" s="9" t="n"/>
+      <c r="O18" s="9" t="n"/>
+      <c r="P18" s="9" t="n"/>
+      <c r="Q18" s="9" t="n"/>
+      <c r="R18" s="9" t="n"/>
+      <c r="S18" s="9" t="n"/>
+      <c r="T18" s="9" t="n"/>
+      <c r="U18" s="9" t="n"/>
+      <c r="V18" s="9" t="n"/>
+      <c r="W18" s="18" t="n"/>
+      <c r="X18" s="9" t="n"/>
+      <c r="Y18" s="9" t="n"/>
+      <c r="Z18" s="9" t="n"/>
+      <c r="AA18" s="9" t="n"/>
+      <c r="AB18" s="9" t="n"/>
+      <c r="AC18" s="9" t="n"/>
+      <c r="AD18" s="9" t="n"/>
+      <c r="AE18" s="9" t="n"/>
     </row>
-    <row r="19" spans="2:31" ht="14.25" customHeight="1">
-      <c r="B19" s="48"/>
-      <c r="C19" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="9"/>
-      <c r="S19" s="9"/>
-      <c r="T19" s="9"/>
-      <c r="U19" s="9"/>
-      <c r="V19" s="9"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="18"/>
-      <c r="Y19" s="9"/>
-      <c r="Z19" s="9"/>
-      <c r="AA19" s="9"/>
-      <c r="AB19" s="9"/>
-      <c r="AC19" s="9"/>
-      <c r="AD19" s="9"/>
-      <c r="AE19" s="9"/>
+    <row r="19" ht="14.25" customHeight="1">
+      <c r="B19" s="123" t="n"/>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>Pruebas de integración</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="9" t="n"/>
+      <c r="I19" s="9" t="n"/>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="9" t="n"/>
+      <c r="L19" s="9" t="n"/>
+      <c r="M19" s="9" t="n"/>
+      <c r="N19" s="9" t="n"/>
+      <c r="O19" s="9" t="n"/>
+      <c r="P19" s="9" t="n"/>
+      <c r="Q19" s="9" t="n"/>
+      <c r="R19" s="9" t="n"/>
+      <c r="S19" s="9" t="n"/>
+      <c r="T19" s="9" t="n"/>
+      <c r="U19" s="9" t="n"/>
+      <c r="V19" s="9" t="n"/>
+      <c r="W19" s="9" t="n"/>
+      <c r="X19" s="18" t="n"/>
+      <c r="Y19" s="9" t="n"/>
+      <c r="Z19" s="9" t="n"/>
+      <c r="AA19" s="9" t="n"/>
+      <c r="AB19" s="9" t="n"/>
+      <c r="AC19" s="9" t="n"/>
+      <c r="AD19" s="9" t="n"/>
+      <c r="AE19" s="9" t="n"/>
     </row>
-    <row r="20" spans="2:31" ht="14.25" customHeight="1">
-      <c r="B20" s="48"/>
-      <c r="C20" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="9"/>
-      <c r="U20" s="9"/>
-      <c r="V20" s="9"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="18"/>
-      <c r="Z20" s="9"/>
-      <c r="AA20" s="9"/>
-      <c r="AB20" s="9"/>
-      <c r="AC20" s="9"/>
-      <c r="AD20" s="9"/>
-      <c r="AE20" s="9"/>
+    <row r="20" ht="14.25" customHeight="1">
+      <c r="B20" s="123" t="n"/>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>Pruebas con usuarios finales</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="9" t="n"/>
+      <c r="I20" s="9" t="n"/>
+      <c r="J20" s="9" t="n"/>
+      <c r="K20" s="9" t="n"/>
+      <c r="L20" s="9" t="n"/>
+      <c r="M20" s="9" t="n"/>
+      <c r="N20" s="9" t="n"/>
+      <c r="O20" s="9" t="n"/>
+      <c r="P20" s="9" t="n"/>
+      <c r="Q20" s="9" t="n"/>
+      <c r="R20" s="9" t="n"/>
+      <c r="S20" s="9" t="n"/>
+      <c r="T20" s="9" t="n"/>
+      <c r="U20" s="9" t="n"/>
+      <c r="V20" s="9" t="n"/>
+      <c r="W20" s="9" t="n"/>
+      <c r="X20" s="9" t="n"/>
+      <c r="Y20" s="18" t="n"/>
+      <c r="Z20" s="9" t="n"/>
+      <c r="AA20" s="9" t="n"/>
+      <c r="AB20" s="9" t="n"/>
+      <c r="AC20" s="9" t="n"/>
+      <c r="AD20" s="9" t="n"/>
+      <c r="AE20" s="9" t="n"/>
     </row>
-    <row r="21" spans="2:31" ht="14.25" customHeight="1">
-      <c r="B21" s="49"/>
-      <c r="C21" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="9"/>
-      <c r="S21" s="9"/>
-      <c r="T21" s="9"/>
-      <c r="U21" s="9"/>
-      <c r="V21" s="9"/>
-      <c r="W21" s="9"/>
-      <c r="X21" s="9"/>
-      <c r="Y21" s="9"/>
-      <c r="Z21" s="18"/>
-      <c r="AA21" s="9"/>
-      <c r="AB21" s="9"/>
-      <c r="AC21" s="9"/>
-      <c r="AD21" s="9"/>
-      <c r="AE21" s="9"/>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="B21" s="124" t="n"/>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>Corrección de errores</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="9" t="n"/>
+      <c r="I21" s="9" t="n"/>
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" s="9" t="n"/>
+      <c r="L21" s="9" t="n"/>
+      <c r="M21" s="9" t="n"/>
+      <c r="N21" s="9" t="n"/>
+      <c r="O21" s="9" t="n"/>
+      <c r="P21" s="9" t="n"/>
+      <c r="Q21" s="9" t="n"/>
+      <c r="R21" s="9" t="n"/>
+      <c r="S21" s="9" t="n"/>
+      <c r="T21" s="9" t="n"/>
+      <c r="U21" s="9" t="n"/>
+      <c r="V21" s="9" t="n"/>
+      <c r="W21" s="9" t="n"/>
+      <c r="X21" s="9" t="n"/>
+      <c r="Y21" s="9" t="n"/>
+      <c r="Z21" s="18" t="n"/>
+      <c r="AA21" s="9" t="n"/>
+      <c r="AB21" s="9" t="n"/>
+      <c r="AC21" s="9" t="n"/>
+      <c r="AD21" s="9" t="n"/>
+      <c r="AE21" s="9" t="n"/>
     </row>
-    <row r="22" spans="2:31" ht="14.25" customHeight="1">
-      <c r="B22" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
-      <c r="Q22" s="9"/>
-      <c r="R22" s="9"/>
-      <c r="S22" s="9"/>
-      <c r="T22" s="9"/>
-      <c r="U22" s="9"/>
-      <c r="V22" s="9"/>
-      <c r="W22" s="9"/>
-      <c r="X22" s="9"/>
-      <c r="Y22" s="9"/>
-      <c r="Z22" s="9"/>
-      <c r="AA22" s="21"/>
-      <c r="AB22" s="21"/>
-      <c r="AC22" s="9"/>
-      <c r="AD22" s="9"/>
-      <c r="AE22" s="9"/>
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="B22" s="122" t="inlineStr">
+        <is>
+          <t>EVALUACION</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>Validación de requerimientos</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="9" t="n"/>
+      <c r="I22" s="9" t="n"/>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="9" t="n"/>
+      <c r="L22" s="9" t="n"/>
+      <c r="M22" s="9" t="n"/>
+      <c r="N22" s="9" t="n"/>
+      <c r="O22" s="9" t="n"/>
+      <c r="P22" s="9" t="n"/>
+      <c r="Q22" s="9" t="n"/>
+      <c r="R22" s="9" t="n"/>
+      <c r="S22" s="9" t="n"/>
+      <c r="T22" s="9" t="n"/>
+      <c r="U22" s="9" t="n"/>
+      <c r="V22" s="9" t="n"/>
+      <c r="W22" s="9" t="n"/>
+      <c r="X22" s="9" t="n"/>
+      <c r="Y22" s="9" t="n"/>
+      <c r="Z22" s="9" t="n"/>
+      <c r="AA22" s="21" t="n"/>
+      <c r="AB22" s="21" t="n"/>
+      <c r="AC22" s="9" t="n"/>
+      <c r="AD22" s="9" t="n"/>
+      <c r="AE22" s="9" t="n"/>
     </row>
-    <row r="23" spans="2:31" ht="27.75" customHeight="1">
-      <c r="B23" s="48"/>
-      <c r="C23" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="9"/>
-      <c r="R23" s="9"/>
-      <c r="S23" s="9"/>
-      <c r="T23" s="9"/>
-      <c r="U23" s="9"/>
-      <c r="V23" s="9"/>
-      <c r="W23" s="9"/>
-      <c r="X23" s="9"/>
-      <c r="Y23" s="9"/>
-      <c r="Z23" s="9"/>
-      <c r="AA23" s="9"/>
-      <c r="AB23" s="21"/>
-      <c r="AC23" s="21"/>
-      <c r="AD23" s="9"/>
-      <c r="AE23" s="9"/>
+    <row r="23" ht="27.75" customHeight="1">
+      <c r="B23" s="123" t="n"/>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>Evaluación de desempeño del prototipo</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
+      <c r="I23" s="9" t="n"/>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="n"/>
+      <c r="L23" s="9" t="n"/>
+      <c r="M23" s="9" t="n"/>
+      <c r="N23" s="9" t="n"/>
+      <c r="O23" s="9" t="n"/>
+      <c r="P23" s="9" t="n"/>
+      <c r="Q23" s="9" t="n"/>
+      <c r="R23" s="9" t="n"/>
+      <c r="S23" s="9" t="n"/>
+      <c r="T23" s="9" t="n"/>
+      <c r="U23" s="9" t="n"/>
+      <c r="V23" s="9" t="n"/>
+      <c r="W23" s="9" t="n"/>
+      <c r="X23" s="9" t="n"/>
+      <c r="Y23" s="9" t="n"/>
+      <c r="Z23" s="9" t="n"/>
+      <c r="AA23" s="9" t="n"/>
+      <c r="AB23" s="21" t="n"/>
+      <c r="AC23" s="21" t="n"/>
+      <c r="AD23" s="9" t="n"/>
+      <c r="AE23" s="9" t="n"/>
     </row>
-    <row r="24" spans="2:31" ht="14.25" customHeight="1">
-      <c r="B24" s="48"/>
-      <c r="C24" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="9"/>
-      <c r="Q24" s="9"/>
-      <c r="R24" s="9"/>
-      <c r="S24" s="9"/>
-      <c r="T24" s="9"/>
-      <c r="U24" s="9"/>
-      <c r="V24" s="9"/>
-      <c r="W24" s="9"/>
-      <c r="X24" s="9"/>
-      <c r="Y24" s="9"/>
-      <c r="Z24" s="9"/>
-      <c r="AA24" s="9"/>
-      <c r="AB24" s="9"/>
-      <c r="AC24" s="9"/>
-      <c r="AD24" s="21"/>
-      <c r="AE24" s="9"/>
+    <row r="24" ht="14.25" customHeight="1">
+      <c r="B24" s="123" t="n"/>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>Informe final de evaluación</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="9" t="n"/>
+      <c r="I24" s="9" t="n"/>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
+      <c r="L24" s="9" t="n"/>
+      <c r="M24" s="9" t="n"/>
+      <c r="N24" s="9" t="n"/>
+      <c r="O24" s="9" t="n"/>
+      <c r="P24" s="9" t="n"/>
+      <c r="Q24" s="9" t="n"/>
+      <c r="R24" s="9" t="n"/>
+      <c r="S24" s="9" t="n"/>
+      <c r="T24" s="9" t="n"/>
+      <c r="U24" s="9" t="n"/>
+      <c r="V24" s="9" t="n"/>
+      <c r="W24" s="9" t="n"/>
+      <c r="X24" s="9" t="n"/>
+      <c r="Y24" s="9" t="n"/>
+      <c r="Z24" s="9" t="n"/>
+      <c r="AA24" s="9" t="n"/>
+      <c r="AB24" s="9" t="n"/>
+      <c r="AC24" s="9" t="n"/>
+      <c r="AD24" s="21" t="n"/>
+      <c r="AE24" s="9" t="n"/>
     </row>
-    <row r="25" spans="2:31" ht="28.5" customHeight="1">
-      <c r="B25" s="49"/>
-      <c r="C25" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
-      <c r="P25" s="9"/>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="9"/>
-      <c r="S25" s="9"/>
-      <c r="T25" s="9"/>
-      <c r="U25" s="9"/>
-      <c r="V25" s="9"/>
-      <c r="W25" s="9"/>
-      <c r="X25" s="9"/>
-      <c r="Y25" s="9"/>
-      <c r="Z25" s="9"/>
-      <c r="AA25" s="9"/>
-      <c r="AB25" s="9"/>
-      <c r="AC25" s="9"/>
-      <c r="AD25" s="9"/>
-      <c r="AE25" s="21"/>
+    <row r="25" ht="28.5" customHeight="1">
+      <c r="B25" s="124" t="n"/>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>Presentación y cierre del proyecto</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="9" t="n"/>
+      <c r="I25" s="9" t="n"/>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="9" t="n"/>
+      <c r="L25" s="9" t="n"/>
+      <c r="M25" s="9" t="n"/>
+      <c r="N25" s="9" t="n"/>
+      <c r="O25" s="9" t="n"/>
+      <c r="P25" s="9" t="n"/>
+      <c r="Q25" s="9" t="n"/>
+      <c r="R25" s="9" t="n"/>
+      <c r="S25" s="9" t="n"/>
+      <c r="T25" s="9" t="n"/>
+      <c r="U25" s="9" t="n"/>
+      <c r="V25" s="9" t="n"/>
+      <c r="W25" s="9" t="n"/>
+      <c r="X25" s="9" t="n"/>
+      <c r="Y25" s="9" t="n"/>
+      <c r="Z25" s="9" t="n"/>
+      <c r="AA25" s="9" t="n"/>
+      <c r="AB25" s="9" t="n"/>
+      <c r="AC25" s="9" t="n"/>
+      <c r="AD25" s="9" t="n"/>
+      <c r="AE25" s="21" t="n"/>
     </row>
-    <row r="26" spans="2:31" ht="14.25" customHeight="1"/>
-    <row r="27" spans="2:31" ht="14.25" customHeight="1"/>
-    <row r="28" spans="2:31" ht="14.25" customHeight="1"/>
-    <row r="29" spans="2:31" ht="14.25" customHeight="1"/>
-    <row r="30" spans="2:31" ht="14.25" customHeight="1"/>
-    <row r="31" spans="2:31" ht="14.25" customHeight="1"/>
-    <row r="32" spans="2:31" ht="14.25" customHeight="1"/>
+    <row r="26" ht="14.25" customHeight="1"/>
+    <row r="27" ht="14.25" customHeight="1"/>
+    <row r="28" ht="14.25" customHeight="1"/>
+    <row r="29" ht="14.25" customHeight="1"/>
+    <row r="30" ht="14.25" customHeight="1"/>
+    <row r="31" ht="14.25" customHeight="1"/>
+    <row r="32" ht="14.25" customHeight="1"/>
     <row r="33" ht="14.25" customHeight="1"/>
     <row r="34" ht="14.25" customHeight="1"/>
     <row r="35" ht="14.25" customHeight="1"/>
@@ -4621,18 +4470,18 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B12:B17"/>
+    <mergeCell ref="B8:B11"/>
     <mergeCell ref="B4:B7"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="B12:B17"/>
     <mergeCell ref="B18:B21"/>
-    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="T2:W2"/>
     <mergeCell ref="X2:AA2"/>
     <mergeCell ref="AB2:AE2"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="L2:O2"/>
     <mergeCell ref="P2:S2"/>
-    <mergeCell ref="T2:W2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -4640,633 +4489,811 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:W1004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:W23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
-    <col min="7" max="8" width="22.7109375" customWidth="1"/>
-    <col min="9" max="10" width="10.7109375" customWidth="1"/>
-    <col min="11" max="11" width="22.7109375" customWidth="1"/>
-    <col min="12" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" customWidth="1"/>
-    <col min="15" max="15" width="18.7109375" customWidth="1"/>
-    <col min="16" max="16" width="10.7109375" customWidth="1"/>
-    <col min="17" max="17" width="23.42578125" customWidth="1"/>
-    <col min="18" max="18" width="21.85546875" customWidth="1"/>
-    <col min="19" max="19" width="22.7109375" customWidth="1"/>
-    <col min="20" max="20" width="23.28515625" customWidth="1"/>
-    <col min="21" max="26" width="10.7109375" customWidth="1"/>
+    <col width="10.7109375" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="10.7109375" customWidth="1" min="3" max="3"/>
+    <col width="16.140625" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10.7109375" customWidth="1" min="6" max="6"/>
+    <col width="22.7109375" customWidth="1" min="7" max="8"/>
+    <col width="10.7109375" customWidth="1" min="9" max="10"/>
+    <col width="22.7109375" customWidth="1" min="11" max="11"/>
+    <col width="10.7109375" customWidth="1" min="12" max="13"/>
+    <col width="15.42578125" customWidth="1" min="14" max="14"/>
+    <col width="18.7109375" customWidth="1" min="15" max="15"/>
+    <col width="10.7109375" customWidth="1" min="16" max="16"/>
+    <col width="23.42578125" customWidth="1" min="17" max="17"/>
+    <col width="21.85546875" customWidth="1" min="18" max="18"/>
+    <col width="22.7109375" customWidth="1" min="19" max="19"/>
+    <col width="23.28515625" customWidth="1" min="20" max="20"/>
+    <col width="10.7109375" customWidth="1" min="21" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="14.25" customHeight="1" thickBot="1"/>
-    <row r="2" spans="2:20" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B2" s="92" t="s">
+    <row r="1" ht="14.25" customHeight="1" thickBot="1"/>
+    <row r="2" ht="14.25" customHeight="1" thickBot="1">
+      <c r="B2" s="125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costos de Hardware </t>
+        </is>
+      </c>
+      <c r="C2" s="126" t="n"/>
+      <c r="D2" s="126" t="n"/>
+      <c r="E2" s="127" t="n"/>
+      <c r="G2" s="128" t="inlineStr">
+        <is>
+          <t>Costos de Software</t>
+        </is>
+      </c>
+      <c r="H2" s="129" t="n"/>
+      <c r="I2" s="130" t="n"/>
+      <c r="K2" s="131" t="inlineStr">
+        <is>
+          <t>Costos de Recurso Humano (estimado por 4 meses de desarrollo)</t>
+        </is>
+      </c>
+      <c r="L2" s="121" t="n"/>
+      <c r="M2" s="121" t="n"/>
+      <c r="N2" s="121" t="n"/>
+      <c r="O2" s="119" t="n"/>
+      <c r="Q2" s="132" t="inlineStr">
+        <is>
+          <t>opciones de los pc para el equipo de desarrollo</t>
+        </is>
+      </c>
+      <c r="R2" s="121" t="n"/>
+      <c r="S2" s="121" t="n"/>
+      <c r="T2" s="119" t="n"/>
+    </row>
+    <row r="3" ht="57.75" customHeight="1" thickBot="1">
+      <c r="B3" s="95" t="n"/>
+      <c r="C3" s="96" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="D3" s="96" t="inlineStr">
+        <is>
+          <t>Precio unitario (COP)</t>
+        </is>
+      </c>
+      <c r="E3" s="97" t="inlineStr">
+        <is>
+          <t>Subtotal (COP)</t>
+        </is>
+      </c>
+      <c r="G3" s="110" t="inlineStr">
+        <is>
+          <t>Herramienta</t>
+        </is>
+      </c>
+      <c r="H3" s="111" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="I3" s="112" t="inlineStr">
+        <is>
+          <t>Costo estimado</t>
+        </is>
+      </c>
+      <c r="K3" s="24" t="inlineStr">
+        <is>
+          <t>Rol</t>
+        </is>
+      </c>
+      <c r="L3" s="23" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="M3" s="23" t="inlineStr">
+        <is>
+          <t>Tiempo (meses)</t>
+        </is>
+      </c>
+      <c r="N3" s="23" t="inlineStr">
+        <is>
+          <t>Costo mensual aprox. (COP)</t>
+        </is>
+      </c>
+      <c r="O3" s="25" t="inlineStr">
+        <is>
+          <t>Subtotal (COP)</t>
+        </is>
+      </c>
+      <c r="Q3" s="26" t="inlineStr">
+        <is>
+          <t>Característica</t>
+        </is>
+      </c>
+      <c r="R3" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Opción 1: Gama de entrada </t>
+        </is>
+      </c>
+      <c r="S3" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Opción 2: Gama media </t>
+        </is>
+      </c>
+      <c r="T3" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Opción 3: Gama alta </t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.25" customHeight="1" thickBot="1">
+      <c r="B4" s="98" t="inlineStr">
+        <is>
+          <t>ESP32 (WiFi + Bluetooth)</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="133" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E4" s="134">
+        <f>C4 * D4</f>
+        <v/>
+      </c>
+      <c r="G4" s="115" t="inlineStr">
+        <is>
+          <t>Arduino IDE</t>
+        </is>
+      </c>
+      <c r="H4" s="116" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="I4" s="135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="27" t="inlineStr">
+        <is>
+          <t>lider</t>
+        </is>
+      </c>
+      <c r="L4" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="N4" s="136" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="O4" s="137">
+        <f>(M4*N4)*L4</f>
+        <v/>
+      </c>
+      <c r="Q4" s="33" t="inlineStr">
+        <is>
+          <t>Rango de precios (COP)</t>
+        </is>
+      </c>
+      <c r="R4" s="34" t="inlineStr">
+        <is>
+          <t>$2.000.000 – $3.500.000</t>
+        </is>
+      </c>
+      <c r="S4" s="34" t="inlineStr">
+        <is>
+          <t>$3.500.000 – $6.000.000</t>
+        </is>
+      </c>
+      <c r="T4" s="34" t="inlineStr">
+        <is>
+          <t>$8.000.000 – $15.000.000+</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="43.5" customHeight="1" thickBot="1">
+      <c r="B5" s="100" t="inlineStr">
+        <is>
+          <t>Medidor de electricidad digital Peacefair PZEM-004T-100A (Sensor)</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="133" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E5" s="134">
+        <f>C5 * D5</f>
+        <v/>
+      </c>
+      <c r="G5" s="113" t="inlineStr">
+        <is>
+          <t>Visual Studio Code</t>
+        </is>
+      </c>
+      <c r="H5" s="114" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="I5" s="135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="27" t="inlineStr">
+        <is>
+          <t>Desarrollador de software</t>
+        </is>
+      </c>
+      <c r="L5" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="N5" s="138" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="O5" s="137">
+        <f>(M5*N5)*L5</f>
+        <v/>
+      </c>
+      <c r="Q5" s="33" t="inlineStr">
+        <is>
+          <t>Procesador (CPU)</t>
+        </is>
+      </c>
+      <c r="R5" s="34" t="inlineStr">
+        <is>
+          <t>Intel Core i5 / AMD Ryzen 5</t>
+        </is>
+      </c>
+      <c r="S5" s="34" t="inlineStr">
+        <is>
+          <t>Intel Core i7 / AMD Ryzen 7</t>
+        </is>
+      </c>
+      <c r="T5" s="34" t="inlineStr">
+        <is>
+          <t>Intel Core i9 / AMD Ryzen 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="39.75" customHeight="1" thickBot="1">
+      <c r="B6" s="98" t="inlineStr">
+        <is>
+          <t>Fuente de alimentación Ac-dc 3.3v Hlk-pm03</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="133" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E6" s="134">
+        <f>C6 * D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="67" t="n"/>
+      <c r="G6" s="108" t="inlineStr">
+        <is>
+          <t>Firebase</t>
+        </is>
+      </c>
+      <c r="H6" s="109" t="inlineStr">
+        <is>
+          <t>Gratis</t>
+        </is>
+      </c>
+      <c r="I6" s="135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="27" t="inlineStr">
+        <is>
+          <t>gestor de bases de datos</t>
+        </is>
+      </c>
+      <c r="L6" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" s="139" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="O6" s="137">
+        <f>(M6*N6)*L6</f>
+        <v/>
+      </c>
+      <c r="Q6" s="33" t="inlineStr">
+        <is>
+          <t>Memoria RAM</t>
+        </is>
+      </c>
+      <c r="R6" s="34" t="inlineStr">
+        <is>
+          <t>16 GB DDR4</t>
+        </is>
+      </c>
+      <c r="S6" s="34" t="inlineStr">
+        <is>
+          <t>32 GB DDR4</t>
+        </is>
+      </c>
+      <c r="T6" s="34" t="inlineStr">
+        <is>
+          <t>64 GB DDR4/DDR5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30.75" customHeight="1" thickBot="1">
+      <c r="B7" s="98" t="inlineStr">
+        <is>
+          <t>Cables Jumpers Macho Macho 20 cm</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="94"/>
-      <c r="G2" s="105" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="106"/>
-      <c r="I2" s="107"/>
-      <c r="K2" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="44"/>
-      <c r="Q2" s="50" t="s">
-        <v>43</v>
-      </c>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="44"/>
+      <c r="D7" s="133" t="n">
+        <v>300</v>
+      </c>
+      <c r="E7" s="134">
+        <f>C7 * D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="67" t="n"/>
+      <c r="G7" s="56" t="n"/>
+      <c r="H7" s="57" t="n"/>
+      <c r="I7" s="140" t="n"/>
+      <c r="K7" s="27" t="inlineStr">
+        <is>
+          <t>analista</t>
+        </is>
+      </c>
+      <c r="L7" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="38" t="n">
+        <v>7</v>
+      </c>
+      <c r="N7" s="139" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="O7" s="137">
+        <f>(M7*N7)*L7</f>
+        <v/>
+      </c>
+      <c r="Q7" s="33" t="inlineStr">
+        <is>
+          <t>Almacenamiento</t>
+        </is>
+      </c>
+      <c r="R7" s="34" t="inlineStr">
+        <is>
+          <t>512 GB SSD (SATA/NVMe)</t>
+        </is>
+      </c>
+      <c r="S7" s="34" t="inlineStr">
+        <is>
+          <t>1 TB SSD</t>
+        </is>
+      </c>
+      <c r="T7" s="34" t="inlineStr">
+        <is>
+          <t>2 TB SSD NVMe</t>
+        </is>
+      </c>
     </row>
-    <row r="3" spans="2:20" ht="57.75" customHeight="1" thickBot="1">
-      <c r="B3" s="95"/>
-      <c r="C3" s="96" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="96" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="97" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="110" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="111" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" s="112" t="s">
-        <v>49</v>
-      </c>
-      <c r="K3" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="L3" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="M3" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="N3" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="O3" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q3" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="R3" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="S3" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="T3" s="26" t="s">
-        <v>56</v>
+    <row r="8" ht="33.75" customHeight="1" thickBot="1">
+      <c r="B8" s="100" t="inlineStr">
+        <is>
+          <t>Cables Jumpers Macho Hembra 20 cm</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="n">
+        <v>40</v>
+      </c>
+      <c r="D8" s="133" t="n">
+        <v>300</v>
+      </c>
+      <c r="E8" s="134">
+        <f>C8 * D8</f>
+        <v/>
+      </c>
+      <c r="K8" s="27" t="inlineStr">
+        <is>
+          <t>Total recurso humano</t>
+        </is>
+      </c>
+      <c r="L8" s="30" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M8" s="30" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N8" s="39" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O8" s="141">
+        <f>SUM(O4:O7)</f>
+        <v/>
+      </c>
+      <c r="Q8" s="33" t="inlineStr">
+        <is>
+          <t>Tarjeta gráfica (GPU)</t>
+        </is>
+      </c>
+      <c r="R8" s="34" t="inlineStr">
+        <is>
+          <t>Integrada</t>
+        </is>
+      </c>
+      <c r="S8" s="34" t="inlineStr">
+        <is>
+          <t>Integrada o dedicada de gama baja (RTX 3050 / RX 6600)</t>
+        </is>
+      </c>
+      <c r="T8" s="34" t="inlineStr">
+        <is>
+          <t>Dedicada de gama alta (RTX 4080 o superior)</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="2:20" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B4" s="98" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="31">
+    <row r="9" ht="60" customHeight="1" thickBot="1">
+      <c r="B9" s="101" t="inlineStr">
+        <is>
+          <t>Cable eléctrico encauchetado de 2x14 AWG</t>
+        </is>
+      </c>
+      <c r="C9" s="102" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="142" t="n">
+        <v>3333</v>
+      </c>
+      <c r="E9" s="143">
+        <f>C9 * D9</f>
+        <v/>
+      </c>
+      <c r="K9" s="56" t="n"/>
+      <c r="L9" s="57" t="n"/>
+      <c r="M9" s="57" t="n"/>
+      <c r="N9" s="57" t="n"/>
+      <c r="O9" s="144" t="n"/>
+      <c r="Q9" s="61" t="inlineStr">
+        <is>
+          <t>Justificación de costos</t>
+        </is>
+      </c>
+      <c r="R9" s="62" t="inlineStr">
+        <is>
+          <t>Componentes accesibles y estándar. No requiere GPU dedicada.</t>
+        </is>
+      </c>
+      <c r="S9" s="62" t="inlineStr">
+        <is>
+          <t>Mayor RAM, CPU más potente, almacenamiento ampliado. Posible inclusión de GPU de gama baja.</t>
+        </is>
+      </c>
+      <c r="T9" s="62" t="inlineStr">
+        <is>
+          <t>Componentes premium: CPU extremo, RAM de gran capacidad, SSD NVMe grande y GPU de última generación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="53.25" customHeight="1" thickBot="1">
+      <c r="B10" s="55" t="inlineStr">
+        <is>
+          <t>Cable calibre 14 rojo y negro</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="29">
-        <v>24000</v>
-      </c>
-      <c r="E4" s="99">
-        <f>C4 * D4</f>
-        <v>24000</v>
-      </c>
-      <c r="G4" s="115" t="s">
-        <v>58</v>
-      </c>
-      <c r="H4" s="116" t="s">
-        <v>59</v>
-      </c>
-      <c r="I4" s="117">
-        <v>0</v>
-      </c>
-      <c r="K4" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="L4" s="28">
+      <c r="D10" s="133" t="n">
+        <v>2400</v>
+      </c>
+      <c r="E10" s="145">
+        <f>C10 * D10</f>
+        <v/>
+      </c>
+      <c r="K10" s="56" t="n"/>
+      <c r="L10" s="57" t="n"/>
+      <c r="M10" s="57" t="n"/>
+      <c r="N10" s="57" t="n"/>
+      <c r="O10" s="144" t="n"/>
+      <c r="Q10" s="61" t="inlineStr">
+        <is>
+          <t>Ejemplos de referencia</t>
+        </is>
+      </c>
+      <c r="R10" s="62" t="inlineStr">
+        <is>
+          <t>Clones y Periféricos, Mercado Libre, Todo Tintas y Suministros</t>
+        </is>
+      </c>
+      <c r="S10" s="62" t="inlineStr">
+        <is>
+          <t>Falabella, Mercado Libre, PC Ware Colombia</t>
+        </is>
+      </c>
+      <c r="T10" s="62" t="inlineStr">
+        <is>
+          <t>Componentes premium: CPU extremo, RAM de gran capacidad, SSD NVMe grande y GPU de última generación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="53.25" customHeight="1" thickBot="1">
+      <c r="B11" s="55" t="inlineStr">
+        <is>
+          <t>Conector Jst Macho-Hembra Xh2.54 Xh2.54mm 4</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="M4" s="31">
-        <v>7</v>
-      </c>
-      <c r="N4" s="32">
-        <v>2000000</v>
-      </c>
-      <c r="O4" s="59">
-        <f>(M4*N4)*L4</f>
-        <v>14000000</v>
-      </c>
-      <c r="Q4" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="R4" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="S4" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="T4" s="34" t="s">
-        <v>64</v>
-      </c>
+      <c r="D11" s="133" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E11" s="145">
+        <f>C11 * D11</f>
+        <v/>
+      </c>
+      <c r="K11" s="56" t="n"/>
+      <c r="L11" s="57" t="n"/>
+      <c r="M11" s="57" t="n"/>
+      <c r="N11" s="57" t="n"/>
+      <c r="O11" s="144" t="n"/>
+      <c r="Q11" s="63" t="n"/>
+      <c r="R11" s="88" t="n"/>
+      <c r="S11" s="89" t="n"/>
+      <c r="T11" s="90" t="n"/>
     </row>
-    <row r="5" spans="2:20" ht="43.5" customHeight="1" thickBot="1">
-      <c r="B5" s="100" t="s">
-        <v>130</v>
-      </c>
-      <c r="C5" s="31">
+    <row r="12" ht="59.25" customHeight="1" thickBot="1">
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t>Cables Jumpers Hembra Hembra 20 cm</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="133" t="n">
+        <v>383</v>
+      </c>
+      <c r="E12" s="145">
+        <f>C12 * D12</f>
+        <v/>
+      </c>
+      <c r="K12" s="56" t="n"/>
+      <c r="L12" s="57" t="n"/>
+      <c r="M12" s="57" t="n"/>
+      <c r="N12" s="57" t="n"/>
+      <c r="O12" s="144" t="n"/>
+      <c r="Q12" s="63" t="inlineStr">
+        <is>
+          <t>opcion elegida</t>
+        </is>
+      </c>
+      <c r="R12" s="146" t="inlineStr">
+        <is>
+          <t>la opción de gama media es la más adecuada porque ofrece un equilibrio entre rendimiento, capacidad de expansión y costo, garantizando que el proyecto de monitoreo eléctrico pueda desarrollarse de manera eficiente y con proyección a futuro.</t>
+        </is>
+      </c>
+      <c r="S12" s="147" t="n"/>
+      <c r="T12" s="148" t="n"/>
+    </row>
+    <row r="13" ht="14.25" customHeight="1" thickBot="1">
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>Caja o carcasa plástica (prototipo)</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="29">
-        <v>70000</v>
-      </c>
-      <c r="E5" s="99">
-        <f t="shared" ref="E5:E15" si="0">C5 * D5</f>
-        <v>70000</v>
-      </c>
-      <c r="G5" s="113" t="s">
-        <v>65</v>
-      </c>
-      <c r="H5" s="114" t="s">
-        <v>59</v>
-      </c>
-      <c r="I5" s="117">
-        <v>0</v>
-      </c>
-      <c r="K5" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="L5" s="28">
-        <v>1</v>
-      </c>
-      <c r="M5" s="31">
-        <v>7</v>
-      </c>
-      <c r="N5" s="35">
-        <v>2500000</v>
-      </c>
-      <c r="O5" s="59">
-        <f t="shared" ref="O5:O7" si="1">(M5*N5)*L5</f>
-        <v>17500000</v>
-      </c>
-      <c r="Q5" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="R5" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="S5" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="T5" s="34" t="s">
-        <v>70</v>
-      </c>
+      <c r="D13" s="133" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E13" s="145">
+        <f>C13 * D13</f>
+        <v/>
+      </c>
+      <c r="Q13" s="77" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="R13" s="149" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="S13" s="150" t="n"/>
+      <c r="T13" s="151" t="n"/>
     </row>
-    <row r="6" spans="2:20" ht="39.75" customHeight="1" thickBot="1">
-      <c r="B6" s="98" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="31">
-        <v>1</v>
-      </c>
-      <c r="D6" s="29">
-        <v>20000</v>
-      </c>
-      <c r="E6" s="99">
-        <f t="shared" si="0"/>
-        <v>20000</v>
-      </c>
-      <c r="F6" s="67"/>
-      <c r="G6" s="108" t="s">
-        <v>71</v>
-      </c>
-      <c r="H6" s="109" t="s">
-        <v>135</v>
-      </c>
-      <c r="I6" s="117">
-        <v>0</v>
-      </c>
-      <c r="K6" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="L6" s="28">
-        <v>1</v>
-      </c>
-      <c r="M6" s="36">
-        <v>4</v>
-      </c>
-      <c r="N6" s="37">
-        <v>1200000</v>
-      </c>
-      <c r="O6" s="59">
-        <f t="shared" si="1"/>
-        <v>4800000</v>
-      </c>
-      <c r="Q6" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="R6" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="S6" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="T6" s="34" t="s">
-        <v>76</v>
-      </c>
+    <row r="14" ht="32.25" customHeight="1" thickBot="1">
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>costos pc del equipo de desarrollo</t>
+        </is>
+      </c>
+      <c r="C14" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="152" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="E14" s="145">
+        <f>C14 * D14</f>
+        <v/>
+      </c>
+      <c r="Q14" s="68" t="n"/>
+      <c r="R14" s="69" t="n"/>
+      <c r="S14" s="69" t="n"/>
+      <c r="T14" s="70" t="n"/>
     </row>
-    <row r="7" spans="2:20" ht="30.75" customHeight="1" thickBot="1">
-      <c r="B7" s="98" t="s">
-        <v>128</v>
-      </c>
-      <c r="C7" s="30">
-        <v>40</v>
-      </c>
-      <c r="D7" s="29">
-        <v>300</v>
-      </c>
-      <c r="E7" s="99">
-        <f t="shared" si="0"/>
-        <v>12000</v>
-      </c>
-      <c r="F7" s="67"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="91"/>
-      <c r="K7" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L7" s="28">
-        <v>1</v>
-      </c>
-      <c r="M7" s="38">
-        <v>7</v>
-      </c>
-      <c r="N7" s="37">
-        <v>1800000</v>
-      </c>
-      <c r="O7" s="59">
-        <f t="shared" si="1"/>
-        <v>12600000</v>
-      </c>
-      <c r="Q7" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="R7" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="S7" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="T7" s="34" t="s">
-        <v>81</v>
-      </c>
+    <row r="15" ht="53.25" customHeight="1" thickBot="1">
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>costos cel del equipo de desarrollo</t>
+        </is>
+      </c>
+      <c r="C15" s="87" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="153" t="n">
+        <v>450000</v>
+      </c>
+      <c r="E15" s="145">
+        <f>C15 * D15</f>
+        <v/>
+      </c>
+      <c r="Q15" s="71" t="n"/>
+      <c r="R15" s="69" t="n"/>
+      <c r="S15" s="72" t="n"/>
+      <c r="T15" s="72" t="n"/>
     </row>
-    <row r="8" spans="2:20" ht="33.75" customHeight="1" thickBot="1">
-      <c r="B8" s="100" t="s">
-        <v>129</v>
-      </c>
-      <c r="C8" s="30">
-        <v>40</v>
-      </c>
-      <c r="D8" s="29">
-        <v>300</v>
-      </c>
-      <c r="E8" s="99">
-        <f t="shared" si="0"/>
-        <v>12000</v>
-      </c>
-      <c r="K8" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="L8" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="M8" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="N8" s="39" t="s">
-        <v>83</v>
-      </c>
-      <c r="O8" s="60">
-        <f>SUM(O4:O7)</f>
-        <v>48900000</v>
-      </c>
-      <c r="Q8" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="R8" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="S8" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="T8" s="34" t="s">
-        <v>87</v>
-      </c>
+    <row r="16" ht="14.25" customHeight="1" thickBot="1">
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>Total aproximado hardware</t>
+        </is>
+      </c>
+      <c r="C16" s="30" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D16" s="30" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E16" s="154">
+        <f>SUM(E4:E15)</f>
+        <v/>
+      </c>
+      <c r="Q16" s="68" t="n"/>
+      <c r="R16" s="73" t="n"/>
+      <c r="S16" s="67" t="n"/>
+      <c r="T16" s="67" t="n"/>
     </row>
-    <row r="9" spans="2:20" ht="60" customHeight="1" thickBot="1">
-      <c r="B9" s="101" t="s">
-        <v>131</v>
-      </c>
-      <c r="C9" s="102">
-        <v>3</v>
-      </c>
-      <c r="D9" s="103">
-        <v>3333</v>
-      </c>
-      <c r="E9" s="104">
-        <f t="shared" si="0"/>
-        <v>9999</v>
-      </c>
-      <c r="K9" s="56"/>
-      <c r="L9" s="57"/>
-      <c r="M9" s="57"/>
-      <c r="N9" s="57"/>
-      <c r="O9" s="58"/>
-      <c r="Q9" s="61" t="s">
-        <v>89</v>
-      </c>
-      <c r="R9" s="62" t="s">
-        <v>90</v>
-      </c>
-      <c r="S9" s="62" t="s">
-        <v>91</v>
-      </c>
-      <c r="T9" s="62" t="s">
-        <v>92</v>
-      </c>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="Q17" s="67" t="n"/>
+      <c r="R17" s="67" t="n"/>
+      <c r="S17" s="67" t="n"/>
+      <c r="T17" s="67" t="n"/>
     </row>
-    <row r="10" spans="2:20" ht="53.25" customHeight="1" thickBot="1">
-      <c r="B10" s="55" t="s">
-        <v>133</v>
-      </c>
-      <c r="C10" s="30">
-        <v>1</v>
-      </c>
-      <c r="D10" s="29">
-        <v>2400</v>
-      </c>
-      <c r="E10" s="86">
-        <f t="shared" si="0"/>
-        <v>2400</v>
-      </c>
-      <c r="K10" s="56"/>
-      <c r="L10" s="57"/>
-      <c r="M10" s="57"/>
-      <c r="N10" s="57"/>
-      <c r="O10" s="58"/>
-      <c r="Q10" s="61" t="s">
-        <v>94</v>
-      </c>
-      <c r="R10" s="62" t="s">
-        <v>95</v>
-      </c>
-      <c r="S10" s="62" t="s">
-        <v>96</v>
-      </c>
-      <c r="T10" s="62" t="s">
-        <v>92</v>
-      </c>
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="Q18" s="155" t="inlineStr">
+        <is>
+          <t>opcion de celular para desarrolladores</t>
+        </is>
+      </c>
+      <c r="R18" s="156" t="n"/>
+      <c r="S18" s="157" t="n"/>
+      <c r="T18" s="67" t="n"/>
     </row>
-    <row r="11" spans="2:20" ht="53.25" customHeight="1" thickBot="1">
-      <c r="B11" s="55" t="s">
-        <v>134</v>
-      </c>
-      <c r="C11" s="30">
-        <v>1</v>
-      </c>
-      <c r="D11" s="29">
-        <v>1300</v>
-      </c>
-      <c r="E11" s="86">
-        <f t="shared" si="0"/>
-        <v>1300</v>
-      </c>
-      <c r="K11" s="56"/>
-      <c r="L11" s="57"/>
-      <c r="M11" s="57"/>
-      <c r="N11" s="57"/>
-      <c r="O11" s="58"/>
-      <c r="Q11" s="63"/>
-      <c r="R11" s="88"/>
-      <c r="S11" s="89"/>
-      <c r="T11" s="90"/>
+    <row r="19" ht="14.25" customHeight="1">
+      <c r="Q19" s="26" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="R19" s="26" t="inlineStr">
+        <is>
+          <t>Rango de precio (COP)</t>
+        </is>
+      </c>
+      <c r="S19" s="26" t="inlineStr">
+        <is>
+          <t>Fuente/Referencia</t>
+        </is>
+      </c>
     </row>
-    <row r="12" spans="2:20" ht="59.25" customHeight="1" thickBot="1">
-      <c r="B12" s="55" t="s">
-        <v>132</v>
-      </c>
-      <c r="C12" s="30">
-        <v>6</v>
-      </c>
-      <c r="D12" s="29">
-        <v>383</v>
-      </c>
-      <c r="E12" s="86">
-        <f>C12 * D12</f>
-        <v>2298</v>
-      </c>
-      <c r="K12" s="56"/>
-      <c r="L12" s="57"/>
-      <c r="M12" s="57"/>
-      <c r="N12" s="57"/>
-      <c r="O12" s="58"/>
-      <c r="Q12" s="63" t="s">
-        <v>98</v>
-      </c>
-      <c r="R12" s="74" t="s">
-        <v>99</v>
-      </c>
-      <c r="S12" s="75"/>
-      <c r="T12" s="76"/>
+    <row r="20" ht="14.25" customHeight="1">
+      <c r="Q20" s="33" t="inlineStr">
+        <is>
+          <t>Xiaomi Redmi 13</t>
+        </is>
+      </c>
+      <c r="R20" s="34" t="inlineStr">
+        <is>
+          <t>$450.000 – $700.000</t>
+        </is>
+      </c>
+      <c r="S20" s="34" t="inlineStr">
+        <is>
+          <t>Mercado Libre y otras tiendas en línea</t>
+        </is>
+      </c>
     </row>
-    <row r="13" spans="2:20" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B13" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="28">
-        <v>1</v>
-      </c>
-      <c r="D13" s="29">
-        <v>20000</v>
-      </c>
-      <c r="E13" s="86">
-        <f t="shared" si="0"/>
-        <v>20000</v>
-      </c>
-      <c r="Q13" s="77" t="s">
-        <v>101</v>
-      </c>
-      <c r="R13" s="78">
-        <v>7000000</v>
-      </c>
-      <c r="S13" s="78"/>
-      <c r="T13" s="78"/>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="Q21" s="33" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy A55</t>
+        </is>
+      </c>
+      <c r="R21" s="34" t="inlineStr">
+        <is>
+          <t>$1.600.000 – $2.200.000</t>
+        </is>
+      </c>
+      <c r="S21" s="34" t="inlineStr">
+        <is>
+          <t>Tiendas oficiales de operadores y minoristas (Mercado Libre, Movistar)</t>
+        </is>
+      </c>
     </row>
-    <row r="14" spans="2:20" ht="32.25" customHeight="1" thickBot="1">
-      <c r="B14" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="C14" s="41">
-        <v>2</v>
-      </c>
-      <c r="D14" s="53">
-        <v>3500000</v>
-      </c>
-      <c r="E14" s="86">
-        <f t="shared" si="0"/>
-        <v>7000000</v>
-      </c>
-      <c r="Q14" s="68"/>
-      <c r="R14" s="69"/>
-      <c r="S14" s="69"/>
-      <c r="T14" s="70"/>
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="Q22" s="42" t="inlineStr">
+        <is>
+          <t>opcion elegida</t>
+        </is>
+      </c>
+      <c r="R22" s="158" t="inlineStr">
+        <is>
+          <t>el Xiaomi Redmi 13 es la mejor elección porque combina bajo costo, compatibilidad tecnológica y accesibilidad en el mercado, cumpliendo con los requerimientos del proyecto sin generar gastos excesivos.</t>
+        </is>
+      </c>
+      <c r="S22" s="148" t="n"/>
+      <c r="W22" s="79" t="n"/>
     </row>
-    <row r="15" spans="2:20" ht="53.25" customHeight="1" thickBot="1">
-      <c r="B15" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="87">
-        <v>2</v>
-      </c>
-      <c r="D15" s="85">
-        <v>450000</v>
-      </c>
-      <c r="E15" s="86">
-        <f t="shared" si="0"/>
+    <row r="23" ht="69" customHeight="1">
+      <c r="Q23" s="80" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="R23" s="159" t="n">
         <v>900000</v>
       </c>
-      <c r="Q15" s="71"/>
-      <c r="R15" s="69"/>
-      <c r="S15" s="72"/>
-      <c r="T15" s="72"/>
+      <c r="S23" s="151" t="n"/>
     </row>
-    <row r="16" spans="2:20" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B16" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="D16" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="E16" s="54">
-        <f>SUM(E4:E15)</f>
-        <v>8073997</v>
-      </c>
-      <c r="Q16" s="68"/>
-      <c r="R16" s="73"/>
-      <c r="S16" s="67"/>
-      <c r="T16" s="67"/>
-    </row>
-    <row r="17" spans="17:23" ht="14.25" customHeight="1">
-      <c r="Q17" s="67"/>
-      <c r="R17" s="67"/>
-      <c r="S17" s="67"/>
-      <c r="T17" s="67"/>
-    </row>
-    <row r="18" spans="17:23" ht="14.25" customHeight="1">
-      <c r="Q18" s="64" t="s">
-        <v>102</v>
-      </c>
-      <c r="R18" s="65"/>
-      <c r="S18" s="66"/>
-      <c r="T18" s="67"/>
-    </row>
-    <row r="19" spans="17:23" ht="14.25" customHeight="1">
-      <c r="Q19" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="R19" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="S19" s="26" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="20" spans="17:23" ht="14.25" customHeight="1">
-      <c r="Q20" s="33" t="s">
-        <v>106</v>
-      </c>
-      <c r="R20" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="S20" s="34" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="21" spans="17:23" ht="14.25" customHeight="1">
-      <c r="Q21" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="R21" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="S21" s="34" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="22" spans="17:23" ht="14.25" customHeight="1">
-      <c r="Q22" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="R22" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="S22" s="34" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="23" spans="17:23" ht="69" customHeight="1">
-      <c r="Q23" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="R23" s="81" t="s">
-        <v>115</v>
-      </c>
-      <c r="S23" s="82"/>
-      <c r="W23" s="79"/>
-    </row>
-    <row r="24" spans="17:23" ht="14.25" customHeight="1">
-      <c r="Q24" s="80" t="s">
-        <v>101</v>
-      </c>
-      <c r="R24" s="83">
-        <v>900000</v>
-      </c>
-      <c r="S24" s="84"/>
-    </row>
-    <row r="25" spans="17:23" ht="14.25" customHeight="1"/>
-    <row r="26" spans="17:23" ht="14.25" customHeight="1"/>
-    <row r="27" spans="17:23" ht="14.25" customHeight="1"/>
-    <row r="28" spans="17:23" ht="14.25" customHeight="1"/>
-    <row r="29" spans="17:23" ht="14.25" customHeight="1"/>
-    <row r="30" spans="17:23" ht="14.25" customHeight="1"/>
-    <row r="31" spans="17:23" ht="14.25" customHeight="1"/>
-    <row r="32" spans="17:23" ht="14.25" customHeight="1"/>
+    <row r="24" ht="14.25" customHeight="1"/>
+    <row r="25" ht="14.25" customHeight="1"/>
+    <row r="26" ht="14.25" customHeight="1"/>
+    <row r="27" ht="14.25" customHeight="1"/>
+    <row r="28" ht="14.25" customHeight="1"/>
+    <row r="29" ht="14.25" customHeight="1"/>
+    <row r="30" ht="14.25" customHeight="1"/>
+    <row r="31" ht="14.25" customHeight="1"/>
+    <row r="32" ht="14.25" customHeight="1"/>
     <row r="33" ht="14.25" customHeight="1"/>
     <row r="34" ht="14.25" customHeight="1"/>
     <row r="35" ht="14.25" customHeight="1"/>
@@ -6241,140 +6268,184 @@
     <row r="1004" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="G2:I2"/>
     <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="G2:I2"/>
     <mergeCell ref="K2:O2"/>
-    <mergeCell ref="Q2:T2"/>
     <mergeCell ref="R12:T12"/>
     <mergeCell ref="R13:T13"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="R22:S22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:H1000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:H6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" customWidth="1"/>
-    <col min="3" max="3" width="21.28515625" customWidth="1"/>
-    <col min="4" max="4" width="22.85546875" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" customWidth="1"/>
-    <col min="6" max="6" width="23.42578125" customWidth="1"/>
-    <col min="7" max="7" width="22.85546875" customWidth="1"/>
-    <col min="8" max="8" width="23.28515625" customWidth="1"/>
-    <col min="9" max="26" width="10.7109375" customWidth="1"/>
+    <col width="10.7109375" customWidth="1" min="1" max="1"/>
+    <col width="11.5703125" customWidth="1" min="2" max="2"/>
+    <col width="21.28515625" customWidth="1" min="3" max="3"/>
+    <col width="22.85546875" customWidth="1" min="4" max="4"/>
+    <col width="10.7109375" customWidth="1" min="5" max="5"/>
+    <col width="23.42578125" customWidth="1" min="6" max="6"/>
+    <col width="22.85546875" customWidth="1" min="7" max="7"/>
+    <col width="23.28515625" customWidth="1" min="8" max="8"/>
+    <col width="10.7109375" customWidth="1" min="9" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="14.25" customHeight="1"/>
-    <row r="2" spans="2:8" ht="14.25" customHeight="1">
-      <c r="B2" s="50" t="s">
-        <v>116</v>
-      </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="44"/>
-      <c r="F2" s="52" t="s">
-        <v>117</v>
-      </c>
-      <c r="G2" s="46"/>
-      <c r="H2" s="44"/>
+    <row r="1" ht="14.25" customHeight="1"/>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="B2" s="132" t="inlineStr">
+        <is>
+          <t>Celulares para Usuarios</t>
+        </is>
+      </c>
+      <c r="C2" s="121" t="n"/>
+      <c r="D2" s="119" t="n"/>
+      <c r="F2" s="160" t="inlineStr">
+        <is>
+          <t>Laptops para Usuarios</t>
+        </is>
+      </c>
+      <c r="G2" s="121" t="n"/>
+      <c r="H2" s="119" t="n"/>
     </row>
-    <row r="3" spans="2:8" ht="14.25" customHeight="1">
-      <c r="B3" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="G3" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>105</v>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
+        <is>
+          <t>Rango de precio (COP)</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>Fuente/Referencia</t>
+        </is>
+      </c>
+      <c r="F3" s="26" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="G3" s="26" t="inlineStr">
+        <is>
+          <t>Rango de precio (COP)</t>
+        </is>
+      </c>
+      <c r="H3" s="26" t="inlineStr">
+        <is>
+          <t>Fuente/Referencia</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="14.25" customHeight="1">
-      <c r="B4" s="33" t="s">
-        <v>106</v>
-      </c>
-      <c r="C4" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="G4" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="H4" s="34" t="s">
-        <v>120</v>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>Xiaomi Redmi 13</t>
+        </is>
+      </c>
+      <c r="C4" s="34" t="inlineStr">
+        <is>
+          <t>$450.000 – $700.000</t>
+        </is>
+      </c>
+      <c r="D4" s="34" t="inlineStr">
+        <is>
+          <t>Mercado Libre y otras tiendas en línea</t>
+        </is>
+      </c>
+      <c r="F4" s="33" t="inlineStr">
+        <is>
+          <t>HP 240 G9 (Core i5, 8 GB RAM, 512 GB SSD)</t>
+        </is>
+      </c>
+      <c r="G4" s="34" t="inlineStr">
+        <is>
+          <t>$2.500.000 – $2.900.000</t>
+        </is>
+      </c>
+      <c r="H4" s="34" t="inlineStr">
+        <is>
+          <t>HP Store Colombia, Mercado Libre</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="14.25" customHeight="1">
-      <c r="B5" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="F5" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="G5" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="H5" s="34" t="s">
-        <v>123</v>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy A55</t>
+        </is>
+      </c>
+      <c r="C5" s="34" t="inlineStr">
+        <is>
+          <t>$1.600.000 – $2.200.000</t>
+        </is>
+      </c>
+      <c r="D5" s="34" t="inlineStr">
+        <is>
+          <t>Tiendas oficiales de operadores y minoristas (Mercado Libre, Movistar)</t>
+        </is>
+      </c>
+      <c r="F5" s="33" t="inlineStr">
+        <is>
+          <t>Dell Inspiron 15 (Core i5, 8 GB RAM)</t>
+        </is>
+      </c>
+      <c r="G5" s="34" t="inlineStr">
+        <is>
+          <t>$1.800.000 – $2.500.000</t>
+        </is>
+      </c>
+      <c r="H5" s="34" t="inlineStr">
+        <is>
+          <t>Dell.es (referencia), Mercado Libre</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="14.25" customHeight="1">
-      <c r="B6" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="C6" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="F6" s="33" t="s">
-        <v>124</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>125</v>
-      </c>
-      <c r="H6" s="34" t="s">
-        <v>126</v>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="B6" s="33" t="n"/>
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="34" t="n"/>
+      <c r="F6" s="33" t="inlineStr">
+        <is>
+          <t>Apple MacBook Air M2 (8 GB RAM, 256 GB SSD)</t>
+        </is>
+      </c>
+      <c r="G6" s="34" t="inlineStr">
+        <is>
+          <t>$4.000.000 – $4.500.000</t>
+        </is>
+      </c>
+      <c r="H6" s="34" t="inlineStr">
+        <is>
+          <t>Éxito, Mercado Libre</t>
+        </is>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="14.25" customHeight="1"/>
-    <row r="8" spans="2:8" ht="14.25" customHeight="1"/>
-    <row r="9" spans="2:8" ht="14.25" customHeight="1"/>
-    <row r="10" spans="2:8" ht="14.25" customHeight="1"/>
-    <row r="11" spans="2:8" ht="14.25" customHeight="1"/>
-    <row r="12" spans="2:8" ht="14.25" customHeight="1"/>
-    <row r="13" spans="2:8" ht="14.25" customHeight="1"/>
-    <row r="14" spans="2:8" ht="14.25" customHeight="1"/>
-    <row r="15" spans="2:8" ht="14.25" customHeight="1"/>
-    <row r="16" spans="2:8" ht="14.25" customHeight="1"/>
+    <row r="7" ht="14.25" customHeight="1"/>
+    <row r="8" ht="14.25" customHeight="1"/>
+    <row r="9" ht="14.25" customHeight="1"/>
+    <row r="10" ht="14.25" customHeight="1"/>
+    <row r="11" ht="14.25" customHeight="1"/>
+    <row r="12" ht="14.25" customHeight="1"/>
+    <row r="13" ht="14.25" customHeight="1"/>
+    <row r="14" ht="14.25" customHeight="1"/>
+    <row r="15" ht="14.25" customHeight="1"/>
+    <row r="16" ht="14.25" customHeight="1"/>
     <row r="17" ht="14.25" customHeight="1"/>
     <row r="18" ht="14.25" customHeight="1"/>
     <row r="19" ht="14.25" customHeight="1"/>
@@ -7361,8 +7432,8 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
